--- a/006/xy_006_data.xlsx
+++ b/006/xy_006_data.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
         <v>1298.225806451613</v>
       </c>
       <c r="C2" t="n">
-        <v>119176736.2600131</v>
+        <v>119176737.0071465</v>
       </c>
     </row>
     <row r="3">
@@ -835,7 +835,7 @@
         <v>1282.677419354839</v>
       </c>
       <c r="C3" t="n">
-        <v>241792625.2117384</v>
+        <v>241792640.3872172</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +846,7 @@
         <v>1271.966666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>172128016.2023249</v>
+        <v>172128030.513173</v>
       </c>
     </row>
     <row r="5">
@@ -857,7 +857,7 @@
         <v>1384.41935483871</v>
       </c>
       <c r="C5" t="n">
-        <v>238658502.4988001</v>
+        <v>238658506.1465502</v>
       </c>
     </row>
     <row r="6">
@@ -868,7 +868,7 @@
         <v>1533.233333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>271074555.7269454</v>
+        <v>271074534.4281673</v>
       </c>
     </row>
     <row r="7">
@@ -879,7 +879,7 @@
         <v>1406.451612903226</v>
       </c>
       <c r="C7" t="n">
-        <v>204999201.1570822</v>
+        <v>204999180.6225777</v>
       </c>
     </row>
     <row r="8">
@@ -890,7 +890,7 @@
         <v>1532.935483870968</v>
       </c>
       <c r="C8" t="n">
-        <v>304536277.5898733</v>
+        <v>304536300.5475119</v>
       </c>
     </row>
     <row r="9">
@@ -901,7 +901,7 @@
         <v>1478.51724137931</v>
       </c>
       <c r="C9" t="n">
-        <v>312717800.0492096</v>
+        <v>312717808.2038879</v>
       </c>
     </row>
     <row r="10">
@@ -912,7 +912,7 @@
         <v>1448.258064516129</v>
       </c>
       <c r="C10" t="n">
-        <v>244389636.1002814</v>
+        <v>244389643.8930793</v>
       </c>
     </row>
     <row r="11">
@@ -923,7 +923,7 @@
         <v>1506.533333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>283940245.984225</v>
+        <v>283940229.4481141</v>
       </c>
     </row>
     <row r="12">
@@ -934,7 +934,7 @@
         <v>1962.709677419355</v>
       </c>
       <c r="C12" t="n">
-        <v>493459850.1314549</v>
+        <v>493459851.9519965</v>
       </c>
     </row>
     <row r="13">
@@ -945,7 +945,7 @@
         <v>1586.166666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>425646464.429812</v>
+        <v>425646461.7016532</v>
       </c>
     </row>
     <row r="14">
@@ -956,7 +956,7 @@
         <v>1516.129032258065</v>
       </c>
       <c r="C14" t="n">
-        <v>467127466.0156012</v>
+        <v>467127451.218462</v>
       </c>
     </row>
     <row r="15">
@@ -967,7 +967,7 @@
         <v>1529.225806451613</v>
       </c>
       <c r="C15" t="n">
-        <v>602732028.2165278</v>
+        <v>602732021.942968</v>
       </c>
     </row>
     <row r="16">
@@ -978,7 +978,7 @@
         <v>1532.1</v>
       </c>
       <c r="C16" t="n">
-        <v>640112888.4446734</v>
+        <v>640112893.6097054</v>
       </c>
     </row>
     <row r="17">
@@ -989,7 +989,7 @@
         <v>1627.064516129032</v>
       </c>
       <c r="C17" t="n">
-        <v>522120923.1866655</v>
+        <v>522120957.7855837</v>
       </c>
     </row>
     <row r="18">
@@ -1000,7 +1000,7 @@
         <v>1879.366666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>1252364754.014606</v>
+        <v>1252364820.939087</v>
       </c>
     </row>
     <row r="19">
@@ -1011,7 +1011,7 @@
         <v>1939.935483870968</v>
       </c>
       <c r="C19" t="n">
-        <v>2170773569.136393</v>
+        <v>2170773464.907056</v>
       </c>
     </row>
     <row r="20">
@@ -1022,7 +1022,7 @@
         <v>2127.193548387097</v>
       </c>
       <c r="C20" t="n">
-        <v>1727593756.597519</v>
+        <v>1727593753.759003</v>
       </c>
     </row>
     <row r="21">
@@ -1033,7 +1033,7 @@
         <v>2087.678571428572</v>
       </c>
       <c r="C21" t="n">
-        <v>2012906144.655027</v>
+        <v>2012906071.050644</v>
       </c>
     </row>
     <row r="22">
@@ -1044,7 +1044,7 @@
         <v>1859.483870967742</v>
       </c>
       <c r="C22" t="n">
-        <v>1582464060.67898</v>
+        <v>1582464114.376856</v>
       </c>
     </row>
     <row r="23">
@@ -1055,7 +1055,7 @@
         <v>1512.6</v>
       </c>
       <c r="C23" t="n">
-        <v>1248475624.477738</v>
+        <v>1248475607.773781</v>
       </c>
     </row>
     <row r="24">
@@ -1066,7 +1066,7 @@
         <v>2128.709677419355</v>
       </c>
       <c r="C24" t="n">
-        <v>2766373700.038346</v>
+        <v>2766373599.863963</v>
       </c>
     </row>
     <row r="25">
@@ -1077,7 +1077,7 @@
         <v>1973.733333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>3969353633.114555</v>
+        <v>3969353568.35647</v>
       </c>
     </row>
     <row r="26">
@@ -1088,7 +1088,7 @@
         <v>1766.677419354839</v>
       </c>
       <c r="C26" t="n">
-        <v>3037884853.216791</v>
+        <v>3037885000.704908</v>
       </c>
     </row>
     <row r="27">
@@ -1099,7 +1099,7 @@
         <v>1769.903225806452</v>
       </c>
       <c r="C27" t="n">
-        <v>2603482709.279517</v>
+        <v>2603482797.420419</v>
       </c>
     </row>
     <row r="28">
@@ -1110,7 +1110,7 @@
         <v>1888.633333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>3139738892.318535</v>
+        <v>3139738921.092033</v>
       </c>
     </row>
     <row r="29">
@@ -1121,7 +1121,7 @@
         <v>2391.677419354839</v>
       </c>
       <c r="C29" t="n">
-        <v>2467356124.213392</v>
+        <v>2467356088.232561</v>
       </c>
     </row>
     <row r="30">
@@ -1132,7 +1132,7 @@
         <v>2574.466666666667</v>
       </c>
       <c r="C30" t="n">
-        <v>2902427418.076107</v>
+        <v>2902427293.988728</v>
       </c>
     </row>
     <row r="31">
@@ -1143,7 +1143,7 @@
         <v>2166.709677419355</v>
       </c>
       <c r="C31" t="n">
-        <v>2395161250.80862</v>
+        <v>2395161410.512543</v>
       </c>
     </row>
     <row r="32">
@@ -1154,7 +1154,7 @@
         <v>2707.193548387097</v>
       </c>
       <c r="C32" t="n">
-        <v>3053681274.172465</v>
+        <v>3053681058.660235</v>
       </c>
     </row>
     <row r="33">
@@ -1165,7 +1165,7 @@
         <v>2507.035714285714</v>
       </c>
       <c r="C33" t="n">
-        <v>4529898946.926518</v>
+        <v>4529898829.469781</v>
       </c>
     </row>
     <row r="34">
@@ -1176,7 +1176,7 @@
         <v>2316.129032258064</v>
       </c>
       <c r="C34" t="n">
-        <v>3955656009.413311</v>
+        <v>3955656275.772549</v>
       </c>
     </row>
     <row r="35">
@@ -1187,7 +1187,7 @@
         <v>1928.9</v>
       </c>
       <c r="C35" t="n">
-        <v>2951766747.552781</v>
+        <v>2951766859.723591</v>
       </c>
     </row>
     <row r="36">
@@ -1198,7 +1198,7 @@
         <v>1936.516129032258</v>
       </c>
       <c r="C36" t="n">
-        <v>3336711009.787906</v>
+        <v>3336711199.892044</v>
       </c>
     </row>
     <row r="37">
@@ -1209,7 +1209,7 @@
         <v>1850.633333333333</v>
       </c>
       <c r="C37" t="n">
-        <v>2643527973.852158</v>
+        <v>2643527824.292228</v>
       </c>
     </row>
     <row r="38">
@@ -1220,7 +1220,7 @@
         <v>1745.838709677419</v>
       </c>
       <c r="C38" t="n">
-        <v>1849653266.87286</v>
+        <v>1849653192.506699</v>
       </c>
     </row>
     <row r="39">
@@ -1231,7 +1231,7 @@
         <v>2394</v>
       </c>
       <c r="C39" t="n">
-        <v>3048666847.979007</v>
+        <v>3048666656.494804</v>
       </c>
     </row>
     <row r="40">
@@ -1242,7 +1242,7 @@
         <v>1712.233333333333</v>
       </c>
       <c r="C40" t="n">
-        <v>2246803825.182463</v>
+        <v>2246803847.557971</v>
       </c>
     </row>
     <row r="41">
@@ -1253,7 +1253,7 @@
         <v>1700.193548387097</v>
       </c>
       <c r="C41" t="n">
-        <v>3244947605.02948</v>
+        <v>3244947761.08294</v>
       </c>
     </row>
     <row r="42">
@@ -1264,7 +1264,7 @@
         <v>1865.533333333333</v>
       </c>
       <c r="C42" t="n">
-        <v>3270224710.370745</v>
+        <v>3270224467.369715</v>
       </c>
     </row>
     <row r="43">
@@ -1275,7 +1275,7 @@
         <v>1616.032258064516</v>
       </c>
       <c r="C43" t="n">
-        <v>2339058629.936319</v>
+        <v>2339058537.711595</v>
       </c>
     </row>
     <row r="44">
@@ -1286,7 +1286,7 @@
         <v>2007.225806451613</v>
       </c>
       <c r="C44" t="n">
-        <v>2863801478.399277</v>
+        <v>2863801396.408808</v>
       </c>
     </row>
     <row r="45">
@@ -1297,7 +1297,7 @@
         <v>1693.642857142857</v>
       </c>
       <c r="C45" t="n">
-        <v>2286165151.008707</v>
+        <v>2286165061.585979</v>
       </c>
     </row>
     <row r="46">
@@ -1308,7 +1308,7 @@
         <v>1730.290322580645</v>
       </c>
       <c r="C46" t="n">
-        <v>2403666268.573534</v>
+        <v>2403666241.122518</v>
       </c>
     </row>
     <row r="47">
@@ -1319,7 +1319,7 @@
         <v>1457.6</v>
       </c>
       <c r="C47" t="n">
-        <v>2077829248.307001</v>
+        <v>2077829157.717659</v>
       </c>
     </row>
     <row r="48">
@@ -1330,7 +1330,7 @@
         <v>1557.741935483871</v>
       </c>
       <c r="C48" t="n">
-        <v>2008990592.429118</v>
+        <v>2008990674.879247</v>
       </c>
     </row>
     <row r="49">
@@ -1341,7 +1341,7 @@
         <v>1509.8</v>
       </c>
       <c r="C49" t="n">
-        <v>1526350616.897392</v>
+        <v>1526350614.668512</v>
       </c>
     </row>
     <row r="50">
@@ -1352,7 +1352,7 @@
         <v>1570.129032258065</v>
       </c>
       <c r="C50" t="n">
-        <v>1589365299.689857</v>
+        <v>1589365146.042911</v>
       </c>
     </row>
     <row r="51">
@@ -1363,7 +1363,7 @@
         <v>1545.516129032258</v>
       </c>
       <c r="C51" t="n">
-        <v>1709685131.761247</v>
+        <v>1709685168.141712</v>
       </c>
     </row>
     <row r="52">
@@ -1374,7 +1374,7 @@
         <v>1475.533333333333</v>
       </c>
       <c r="C52" t="n">
-        <v>1398975235.425663</v>
+        <v>1398975225.697899</v>
       </c>
     </row>
     <row r="53">
@@ -1385,7 +1385,7 @@
         <v>1672.225806451613</v>
       </c>
       <c r="C53" t="n">
-        <v>1578080612.629849</v>
+        <v>1578080635.129348</v>
       </c>
     </row>
     <row r="54">
@@ -1396,7 +1396,7 @@
         <v>1982.8</v>
       </c>
       <c r="C54" t="n">
-        <v>1909638747.025585</v>
+        <v>1909638760.464764</v>
       </c>
     </row>
     <row r="55">
@@ -1407,7 +1407,7 @@
         <v>1901.58064516129</v>
       </c>
       <c r="C55" t="n">
-        <v>1741241933.711097</v>
+        <v>1741241886.876606</v>
       </c>
     </row>
     <row r="56">
@@ -1418,7 +1418,7 @@
         <v>1939.709677419355</v>
       </c>
       <c r="C56" t="n">
-        <v>1772561634.89923</v>
+        <v>1772561646.208264</v>
       </c>
     </row>
     <row r="57">
@@ -1429,7 +1429,7 @@
         <v>2214.655172413793</v>
       </c>
       <c r="C57" t="n">
-        <v>4268220172.323026</v>
+        <v>4268220182.537079</v>
       </c>
     </row>
     <row r="58">
@@ -1440,7 +1440,7 @@
         <v>1884.709677419355</v>
       </c>
       <c r="C58" t="n">
-        <v>4310317333.79416</v>
+        <v>4310317335.106243</v>
       </c>
     </row>
     <row r="59">
@@ -1451,7 +1451,7 @@
         <v>2553.6</v>
       </c>
       <c r="C59" t="n">
-        <v>3663569498.108727</v>
+        <v>3663569546.119599</v>
       </c>
     </row>
     <row r="60">
@@ -1462,7 +1462,7 @@
         <v>2908.16129032258</v>
       </c>
       <c r="C60" t="n">
-        <v>5221682700.204563</v>
+        <v>5221682370.371246</v>
       </c>
     </row>
     <row r="61">
@@ -1473,7 +1473,7 @@
         <v>2159.2</v>
       </c>
       <c r="C61" t="n">
-        <v>4001159677.738016</v>
+        <v>4001159629.920266</v>
       </c>
     </row>
     <row r="62">
@@ -1484,7 +1484,7 @@
         <v>2442.258064516129</v>
       </c>
       <c r="C62" t="n">
-        <v>3743314322.038477</v>
+        <v>3743314088.924234</v>
       </c>
     </row>
     <row r="63">
@@ -1495,7 +1495,7 @@
         <v>2704.741935483871</v>
       </c>
       <c r="C63" t="n">
-        <v>5538476188.02116</v>
+        <v>5538476063.250587</v>
       </c>
     </row>
     <row r="64">
@@ -1506,7 +1506,7 @@
         <v>6176.033333333334</v>
       </c>
       <c r="C64" t="n">
-        <v>9591019639.002119</v>
+        <v>9591020034.210024</v>
       </c>
     </row>
     <row r="65">
@@ -1517,7 +1517,7 @@
         <v>2910.16129032258</v>
       </c>
       <c r="C65" t="n">
-        <v>4914765474.741329</v>
+        <v>4914765573.11873</v>
       </c>
     </row>
     <row r="66">
@@ -1528,7 +1528,7 @@
         <v>2748.8</v>
       </c>
       <c r="C66" t="n">
-        <v>5055653202.607536</v>
+        <v>5055653229.122925</v>
       </c>
     </row>
     <row r="67">
@@ -1539,7 +1539,7 @@
         <v>2842.096774193548</v>
       </c>
       <c r="C67" t="n">
-        <v>3064971919.366837</v>
+        <v>3064972020.195354</v>
       </c>
     </row>
     <row r="68">
@@ -1550,7 +1550,7 @@
         <v>2434.225806451613</v>
       </c>
       <c r="C68" t="n">
-        <v>4272179401.799252</v>
+        <v>4272179455.635673</v>
       </c>
     </row>
     <row r="69">
@@ -1561,7 +1561,7 @@
         <v>2552.964285714286</v>
       </c>
       <c r="C69" t="n">
-        <v>4993958833.023874</v>
+        <v>4993958986.845518</v>
       </c>
     </row>
     <row r="70">
@@ -1572,7 +1572,7 @@
         <v>2229.58064516129</v>
       </c>
       <c r="C70" t="n">
-        <v>4230832291.022425</v>
+        <v>4230832190.56005</v>
       </c>
     </row>
     <row r="71">
@@ -1583,7 +1583,7 @@
         <v>2665.766666666667</v>
       </c>
       <c r="C71" t="n">
-        <v>4821919124.92625</v>
+        <v>4821919007.947468</v>
       </c>
     </row>
     <row r="72">
@@ -1594,7 +1594,7 @@
         <v>1874.451612903226</v>
       </c>
       <c r="C72" t="n">
-        <v>5226246480.539894</v>
+        <v>5226246439.409256</v>
       </c>
     </row>
     <row r="73">
@@ -1605,7 +1605,7 @@
         <v>2106.2</v>
       </c>
       <c r="C73" t="n">
-        <v>8455848790.680625</v>
+        <v>8455848799.906297</v>
       </c>
     </row>
     <row r="74">
@@ -1616,7 +1616,7 @@
         <v>3009.967741935484</v>
       </c>
       <c r="C74" t="n">
-        <v>7250314867.30067</v>
+        <v>7250315233.622869</v>
       </c>
     </row>
     <row r="75">
@@ -1627,7 +1627,7 @@
         <v>2687.83870967742</v>
       </c>
       <c r="C75" t="n">
-        <v>6041826715.214469</v>
+        <v>6041826386.172901</v>
       </c>
     </row>
     <row r="76">
@@ -1638,7 +1638,7 @@
         <v>2291.7</v>
       </c>
       <c r="C76" t="n">
-        <v>5187963222.653525</v>
+        <v>5187963508.786974</v>
       </c>
     </row>
     <row r="77">
@@ -1649,7 +1649,7 @@
         <v>2480</v>
       </c>
       <c r="C77" t="n">
-        <v>5246803830.446607</v>
+        <v>5246804111.124493</v>
       </c>
     </row>
     <row r="78">
@@ -1660,7 +1660,7 @@
         <v>3524.033333333333</v>
       </c>
       <c r="C78" t="n">
-        <v>15717939036.46941</v>
+        <v>15717939150.24885</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         <v>2796.483870967742</v>
       </c>
       <c r="C79" t="n">
-        <v>14946670458.4856</v>
+        <v>14946669691.22011</v>
       </c>
     </row>
     <row r="80">
@@ -1682,7 +1682,7 @@
         <v>3098.774193548387</v>
       </c>
       <c r="C80" t="n">
-        <v>13493538718.10045</v>
+        <v>13493538590.90481</v>
       </c>
     </row>
     <row r="81">
@@ -1693,7 +1693,7 @@
         <v>3629</v>
       </c>
       <c r="C81" t="n">
-        <v>13743048528.34902</v>
+        <v>13743048357.92401</v>
       </c>
     </row>
     <row r="82">
@@ -1704,7 +1704,7 @@
         <v>2717.83870967742</v>
       </c>
       <c r="C82" t="n">
-        <v>12664921561.98137</v>
+        <v>12664921353.59582</v>
       </c>
     </row>
     <row r="83">
@@ -1715,7 +1715,7 @@
         <v>2543.733333333333</v>
       </c>
       <c r="C83" t="n">
-        <v>12069929311.44285</v>
+        <v>12069929531.71988</v>
       </c>
     </row>
     <row r="84">
@@ -1726,7 +1726,7 @@
         <v>2563.741935483871</v>
       </c>
       <c r="C84" t="n">
-        <v>11649542571.27498</v>
+        <v>11649542739.25881</v>
       </c>
     </row>
     <row r="85">
@@ -1737,7 +1737,7 @@
         <v>2212.2</v>
       </c>
       <c r="C85" t="n">
-        <v>8489482564.836275</v>
+        <v>8489482874.203092</v>
       </c>
     </row>
     <row r="86">
@@ -1748,7 +1748,7 @@
         <v>2478.870967741936</v>
       </c>
       <c r="C86" t="n">
-        <v>8610809762.630081</v>
+        <v>8610809537.190723</v>
       </c>
     </row>
     <row r="87">
@@ -1759,7 +1759,7 @@
         <v>2578.41935483871</v>
       </c>
       <c r="C87" t="n">
-        <v>9233110416.166264</v>
+        <v>9233110943.686735</v>
       </c>
     </row>
     <row r="88">
@@ -1770,7 +1770,7 @@
         <v>3461.933333333333</v>
       </c>
       <c r="C88" t="n">
-        <v>8220308153.778984</v>
+        <v>8220307964.633487</v>
       </c>
     </row>
     <row r="89">
@@ -1781,7 +1781,7 @@
         <v>2781.032258064516</v>
       </c>
       <c r="C89" t="n">
-        <v>7390135201.267742</v>
+        <v>7390134873.710088</v>
       </c>
     </row>
     <row r="90">
@@ -1792,7 +1792,7 @@
         <v>2871.766666666667</v>
       </c>
       <c r="C90" t="n">
-        <v>7689883999.936604</v>
+        <v>7689883749.582563</v>
       </c>
     </row>
     <row r="91">
@@ -1803,7 +1803,7 @@
         <v>2108.83870967742</v>
       </c>
       <c r="C91" t="n">
-        <v>6933557906.997817</v>
+        <v>6933557571.203413</v>
       </c>
     </row>
     <row r="92">
@@ -1814,7 +1814,7 @@
         <v>2195.83870967742</v>
       </c>
       <c r="C92" t="n">
-        <v>8221944933.383608</v>
+        <v>8221944728.960037</v>
       </c>
     </row>
     <row r="93">
@@ -1825,7 +1825,7 @@
         <v>2518.964285714286</v>
       </c>
       <c r="C93" t="n">
-        <v>12078125537.09773</v>
+        <v>12078125594.63622</v>
       </c>
     </row>
     <row r="94">
@@ -1836,7 +1836,7 @@
         <v>3074.193548387097</v>
       </c>
       <c r="C94" t="n">
-        <v>12270776489.82504</v>
+        <v>12270776759.34808</v>
       </c>
     </row>
     <row r="95">
@@ -1847,7 +1847,7 @@
         <v>2653.633333333333</v>
       </c>
       <c r="C95" t="n">
-        <v>10592547114.8512</v>
+        <v>10592546983.15068</v>
       </c>
     </row>
     <row r="96">
@@ -1858,7 +1858,7 @@
         <v>7040.548387096775</v>
       </c>
       <c r="C96" t="n">
-        <v>17384080881.73069</v>
+        <v>17384081108.25114</v>
       </c>
     </row>
     <row r="97">
@@ -1869,7 +1869,7 @@
         <v>5477</v>
       </c>
       <c r="C97" t="n">
-        <v>20510416229.61734</v>
+        <v>20510416617.15553</v>
       </c>
     </row>
     <row r="98">
@@ -1880,7 +1880,7 @@
         <v>3981.806451612903</v>
       </c>
       <c r="C98" t="n">
-        <v>19516665404.41132</v>
+        <v>19516666394.23046</v>
       </c>
     </row>
     <row r="99">
@@ -1891,7 +1891,7 @@
         <v>5717.967741935484</v>
       </c>
       <c r="C99" t="n">
-        <v>26892085442.28114</v>
+        <v>26892085282.89082</v>
       </c>
     </row>
     <row r="100">
@@ -1902,7 +1902,7 @@
         <v>5511</v>
       </c>
       <c r="C100" t="n">
-        <v>18956786193.91842</v>
+        <v>18956786256.3139</v>
       </c>
     </row>
     <row r="101">
@@ -1913,7 +1913,7 @@
         <v>4307.548387096775</v>
       </c>
       <c r="C101" t="n">
-        <v>20004110614.40416</v>
+        <v>20004110873.25478</v>
       </c>
     </row>
     <row r="102">
@@ -1924,7 +1924,7 @@
         <v>4725.066666666667</v>
       </c>
       <c r="C102" t="n">
-        <v>20662350586.79599</v>
+        <v>20662350889.41992</v>
       </c>
     </row>
     <row r="103">
@@ -1935,7 +1935,7 @@
         <v>5359.677419354839</v>
       </c>
       <c r="C103" t="n">
-        <v>17729040238.73692</v>
+        <v>17729040188.06858</v>
       </c>
     </row>
     <row r="104">
@@ -1946,7 +1946,7 @@
         <v>6081.290322580645</v>
       </c>
       <c r="C104" t="n">
-        <v>25939419774.41552</v>
+        <v>25939419759.39923</v>
       </c>
     </row>
     <row r="105">
@@ -1957,7 +1957,7 @@
         <v>16719.93103448276</v>
       </c>
       <c r="C105" t="n">
-        <v>40100316620.61958</v>
+        <v>40100317471.08879</v>
       </c>
     </row>
     <row r="106">
@@ -1968,7 +1968,7 @@
         <v>11840.38709677419</v>
       </c>
       <c r="C106" t="n">
-        <v>54116072750.16327</v>
+        <v>54116072605.90096</v>
       </c>
     </row>
     <row r="107">
@@ -1979,7 +1979,7 @@
         <v>6815</v>
       </c>
       <c r="C107" t="n">
-        <v>38842930826.68027</v>
+        <v>38842932353.45078</v>
       </c>
     </row>
     <row r="108">
@@ -1990,7 +1990,7 @@
         <v>8506.225806451614</v>
       </c>
       <c r="C108" t="n">
-        <v>42766666588.00021</v>
+        <v>42766667754.27766</v>
       </c>
     </row>
     <row r="109">
@@ -2001,7 +2001,7 @@
         <v>20799.36666666666</v>
       </c>
       <c r="C109" t="n">
-        <v>48378555652.19691</v>
+        <v>48378555897.5914</v>
       </c>
     </row>
     <row r="110">
@@ -2012,7 +2012,7 @@
         <v>6610.064516129032</v>
       </c>
       <c r="C110" t="n">
-        <v>35004278111.62473</v>
+        <v>35004278763.2421</v>
       </c>
     </row>
     <row r="111">
@@ -2023,7 +2023,7 @@
         <v>8099.516129032259</v>
       </c>
       <c r="C111" t="n">
-        <v>42578841798.59255</v>
+        <v>42578842389.77814</v>
       </c>
     </row>
     <row r="112">
@@ -2034,7 +2034,7 @@
         <v>6939.6</v>
       </c>
       <c r="C112" t="n">
-        <v>35817074857.85065</v>
+        <v>35817076481.33392</v>
       </c>
     </row>
     <row r="113">
@@ -2045,7 +2045,7 @@
         <v>7433.806451612903</v>
       </c>
       <c r="C113" t="n">
-        <v>32600566148.4255</v>
+        <v>32600565649.69154</v>
       </c>
     </row>
     <row r="114">
@@ -2056,7 +2056,7 @@
         <v>9167.799999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>31985011735.90187</v>
+        <v>31985012267.4627</v>
       </c>
     </row>
     <row r="115">
@@ -2067,7 +2067,7 @@
         <v>7653.322580645161</v>
       </c>
       <c r="C115" t="n">
-        <v>26515688268.10477</v>
+        <v>26515687818.22706</v>
       </c>
     </row>
     <row r="116">
@@ -2078,7 +2078,7 @@
         <v>14017.22580645161</v>
       </c>
       <c r="C116" t="n">
-        <v>39289486358.55137</v>
+        <v>39289486511.36562</v>
       </c>
     </row>
     <row r="117">
@@ -2089,7 +2089,7 @@
         <v>7292.892857142857</v>
       </c>
       <c r="C117" t="n">
-        <v>32133024139.17048</v>
+        <v>32133024447.99046</v>
       </c>
     </row>
     <row r="118">
@@ -2100,7 +2100,7 @@
         <v>5586.193548387097</v>
       </c>
       <c r="C118" t="n">
-        <v>33609223033.66285</v>
+        <v>33609222854.53938</v>
       </c>
     </row>
     <row r="119">
@@ -2111,7 +2111,7 @@
         <v>6057.533333333334</v>
       </c>
       <c r="C119" t="n">
-        <v>33845541376.64889</v>
+        <v>33845541809.23596</v>
       </c>
     </row>
     <row r="120">
@@ -2122,7 +2122,7 @@
         <v>4955.83870967742</v>
       </c>
       <c r="C120" t="n">
-        <v>29082742301.91574</v>
+        <v>29082741672.72074</v>
       </c>
     </row>
     <row r="121">
@@ -2133,7 +2133,7 @@
         <v>4150.066666666667</v>
       </c>
       <c r="C121" t="n">
-        <v>27853410382.11868</v>
+        <v>27853411119.15093</v>
       </c>
     </row>
     <row r="122">
@@ -2144,7 +2144,7 @@
         <v>9500.548387096775</v>
       </c>
       <c r="C122" t="n">
-        <v>27389922873.85192</v>
+        <v>27389921193.10247</v>
       </c>
     </row>
     <row r="123">
@@ -2155,7 +2155,7 @@
         <v>7495.870967741936</v>
       </c>
       <c r="C123" t="n">
-        <v>30709050730.9651</v>
+        <v>30709051255.2948</v>
       </c>
     </row>
     <row r="124">
@@ -2166,7 +2166,7 @@
         <v>6704.133333333333</v>
       </c>
       <c r="C124" t="n">
-        <v>32524643561.45914</v>
+        <v>32524643145.8273</v>
       </c>
     </row>
     <row r="125">
@@ -2177,7 +2177,7 @@
         <v>10377.61290322581</v>
       </c>
       <c r="C125" t="n">
-        <v>33105939647.43792</v>
+        <v>33105939936.52052</v>
       </c>
     </row>
     <row r="126">
@@ -2188,7 +2188,7 @@
         <v>12848.83333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>40842151404.3355</v>
+        <v>40842150158.30857</v>
       </c>
     </row>
     <row r="127">
@@ -2199,7 +2199,7 @@
         <v>7957.709677419355</v>
       </c>
       <c r="C127" t="n">
-        <v>29884818995.19355</v>
+        <v>29884819259.77242</v>
       </c>
     </row>
     <row r="128">
@@ -2210,7 +2210,7 @@
         <v>7034.967741935484</v>
       </c>
       <c r="C128" t="n">
-        <v>30639420819.37004</v>
+        <v>30639420705.97175</v>
       </c>
     </row>
     <row r="129">
@@ -2221,7 +2221,7 @@
         <v>6380.107142857143</v>
       </c>
       <c r="C129" t="n">
-        <v>36431005418.7243</v>
+        <v>36431005459.34392</v>
       </c>
     </row>
     <row r="130">
@@ -2232,7 +2232,7 @@
         <v>5631.548387096775</v>
       </c>
       <c r="C130" t="n">
-        <v>32571482558.46391</v>
+        <v>32571482282.69625</v>
       </c>
     </row>
     <row r="131">
@@ -35014,7 +35014,7 @@
         <v>42186</v>
       </c>
       <c r="B2" t="n">
-        <v>119176736.2600131</v>
+        <v>119176737.0071465</v>
       </c>
     </row>
     <row r="3">
@@ -35022,7 +35022,7 @@
         <v>42217</v>
       </c>
       <c r="B3" t="n">
-        <v>241792625.2117384</v>
+        <v>241792640.3872172</v>
       </c>
     </row>
     <row r="4">
@@ -35030,7 +35030,7 @@
         <v>42248</v>
       </c>
       <c r="B4" t="n">
-        <v>172128016.2023249</v>
+        <v>172128030.513173</v>
       </c>
     </row>
     <row r="5">
@@ -35038,7 +35038,7 @@
         <v>42278</v>
       </c>
       <c r="B5" t="n">
-        <v>238658502.4988001</v>
+        <v>238658506.1465502</v>
       </c>
     </row>
     <row r="6">
@@ -35046,7 +35046,7 @@
         <v>42309</v>
       </c>
       <c r="B6" t="n">
-        <v>271074555.7269454</v>
+        <v>271074534.4281673</v>
       </c>
     </row>
     <row r="7">
@@ -35054,7 +35054,7 @@
         <v>42339</v>
       </c>
       <c r="B7" t="n">
-        <v>204999201.1570822</v>
+        <v>204999180.6225777</v>
       </c>
     </row>
     <row r="8">
@@ -35062,7 +35062,7 @@
         <v>42370</v>
       </c>
       <c r="B8" t="n">
-        <v>304536277.5898733</v>
+        <v>304536300.5475119</v>
       </c>
     </row>
     <row r="9">
@@ -35070,7 +35070,7 @@
         <v>42401</v>
       </c>
       <c r="B9" t="n">
-        <v>312717800.0492096</v>
+        <v>312717808.2038879</v>
       </c>
     </row>
     <row r="10">
@@ -35078,7 +35078,7 @@
         <v>42430</v>
       </c>
       <c r="B10" t="n">
-        <v>244389636.1002814</v>
+        <v>244389643.8930793</v>
       </c>
     </row>
     <row r="11">
@@ -35086,7 +35086,7 @@
         <v>42461</v>
       </c>
       <c r="B11" t="n">
-        <v>283940245.984225</v>
+        <v>283940229.4481141</v>
       </c>
     </row>
     <row r="12">
@@ -35094,7 +35094,7 @@
         <v>42491</v>
       </c>
       <c r="B12" t="n">
-        <v>493459850.1314549</v>
+        <v>493459851.9519965</v>
       </c>
     </row>
     <row r="13">
@@ -35102,7 +35102,7 @@
         <v>42522</v>
       </c>
       <c r="B13" t="n">
-        <v>425646464.429812</v>
+        <v>425646461.7016532</v>
       </c>
     </row>
     <row r="14">
@@ -35110,7 +35110,7 @@
         <v>42552</v>
       </c>
       <c r="B14" t="n">
-        <v>467127466.0156012</v>
+        <v>467127451.218462</v>
       </c>
     </row>
     <row r="15">
@@ -35118,7 +35118,7 @@
         <v>42583</v>
       </c>
       <c r="B15" t="n">
-        <v>602732028.2165278</v>
+        <v>602732021.942968</v>
       </c>
     </row>
     <row r="16">
@@ -35126,7 +35126,7 @@
         <v>42614</v>
       </c>
       <c r="B16" t="n">
-        <v>640112888.4446734</v>
+        <v>640112893.6097054</v>
       </c>
     </row>
     <row r="17">
@@ -35134,7 +35134,7 @@
         <v>42644</v>
       </c>
       <c r="B17" t="n">
-        <v>522120923.1866655</v>
+        <v>522120957.7855837</v>
       </c>
     </row>
     <row r="18">
@@ -35142,7 +35142,7 @@
         <v>42675</v>
       </c>
       <c r="B18" t="n">
-        <v>1252364754.014606</v>
+        <v>1252364820.939087</v>
       </c>
     </row>
     <row r="19">
@@ -35150,7 +35150,7 @@
         <v>42705</v>
       </c>
       <c r="B19" t="n">
-        <v>2170773569.136393</v>
+        <v>2170773464.907056</v>
       </c>
     </row>
     <row r="20">
@@ -35158,7 +35158,7 @@
         <v>42736</v>
       </c>
       <c r="B20" t="n">
-        <v>1727593756.597519</v>
+        <v>1727593753.759003</v>
       </c>
     </row>
     <row r="21">
@@ -35166,7 +35166,7 @@
         <v>42767</v>
       </c>
       <c r="B21" t="n">
-        <v>2012906144.655027</v>
+        <v>2012906071.050644</v>
       </c>
     </row>
     <row r="22">
@@ -35174,7 +35174,7 @@
         <v>42795</v>
       </c>
       <c r="B22" t="n">
-        <v>1582464060.67898</v>
+        <v>1582464114.376856</v>
       </c>
     </row>
     <row r="23">
@@ -35182,7 +35182,7 @@
         <v>42826</v>
       </c>
       <c r="B23" t="n">
-        <v>1248475624.477738</v>
+        <v>1248475607.773781</v>
       </c>
     </row>
     <row r="24">
@@ -35190,7 +35190,7 @@
         <v>42856</v>
       </c>
       <c r="B24" t="n">
-        <v>2766373700.038346</v>
+        <v>2766373599.863963</v>
       </c>
     </row>
     <row r="25">
@@ -35198,7 +35198,7 @@
         <v>42887</v>
       </c>
       <c r="B25" t="n">
-        <v>3969353633.114555</v>
+        <v>3969353568.35647</v>
       </c>
     </row>
     <row r="26">
@@ -35206,7 +35206,7 @@
         <v>42917</v>
       </c>
       <c r="B26" t="n">
-        <v>3037884853.216791</v>
+        <v>3037885000.704908</v>
       </c>
     </row>
     <row r="27">
@@ -35214,7 +35214,7 @@
         <v>42948</v>
       </c>
       <c r="B27" t="n">
-        <v>2603482709.279517</v>
+        <v>2603482797.420419</v>
       </c>
     </row>
     <row r="28">
@@ -35222,7 +35222,7 @@
         <v>42979</v>
       </c>
       <c r="B28" t="n">
-        <v>3139738892.318535</v>
+        <v>3139738921.092033</v>
       </c>
     </row>
     <row r="29">
@@ -35230,7 +35230,7 @@
         <v>43009</v>
       </c>
       <c r="B29" t="n">
-        <v>2467356124.213392</v>
+        <v>2467356088.232561</v>
       </c>
     </row>
     <row r="30">
@@ -35238,7 +35238,7 @@
         <v>43040</v>
       </c>
       <c r="B30" t="n">
-        <v>2902427418.076107</v>
+        <v>2902427293.988728</v>
       </c>
     </row>
     <row r="31">
@@ -35246,7 +35246,7 @@
         <v>43070</v>
       </c>
       <c r="B31" t="n">
-        <v>2395161250.80862</v>
+        <v>2395161410.512543</v>
       </c>
     </row>
     <row r="32">
@@ -35254,7 +35254,7 @@
         <v>43101</v>
       </c>
       <c r="B32" t="n">
-        <v>3053681274.172465</v>
+        <v>3053681058.660235</v>
       </c>
     </row>
     <row r="33">
@@ -35262,7 +35262,7 @@
         <v>43132</v>
       </c>
       <c r="B33" t="n">
-        <v>4529898946.926518</v>
+        <v>4529898829.469781</v>
       </c>
     </row>
     <row r="34">
@@ -35270,7 +35270,7 @@
         <v>43160</v>
       </c>
       <c r="B34" t="n">
-        <v>3955656009.413311</v>
+        <v>3955656275.772549</v>
       </c>
     </row>
     <row r="35">
@@ -35278,7 +35278,7 @@
         <v>43191</v>
       </c>
       <c r="B35" t="n">
-        <v>2951766747.552781</v>
+        <v>2951766859.723591</v>
       </c>
     </row>
     <row r="36">
@@ -35286,7 +35286,7 @@
         <v>43221</v>
       </c>
       <c r="B36" t="n">
-        <v>3336711009.787906</v>
+        <v>3336711199.892044</v>
       </c>
     </row>
     <row r="37">
@@ -35294,7 +35294,7 @@
         <v>43252</v>
       </c>
       <c r="B37" t="n">
-        <v>2643527973.852158</v>
+        <v>2643527824.292228</v>
       </c>
     </row>
     <row r="38">
@@ -35302,7 +35302,7 @@
         <v>43282</v>
       </c>
       <c r="B38" t="n">
-        <v>1849653266.87286</v>
+        <v>1849653192.506699</v>
       </c>
     </row>
     <row r="39">
@@ -35310,7 +35310,7 @@
         <v>43313</v>
       </c>
       <c r="B39" t="n">
-        <v>3048666847.979007</v>
+        <v>3048666656.494804</v>
       </c>
     </row>
     <row r="40">
@@ -35318,7 +35318,7 @@
         <v>43344</v>
       </c>
       <c r="B40" t="n">
-        <v>2246803825.182463</v>
+        <v>2246803847.557971</v>
       </c>
     </row>
     <row r="41">
@@ -35326,7 +35326,7 @@
         <v>43374</v>
       </c>
       <c r="B41" t="n">
-        <v>3244947605.02948</v>
+        <v>3244947761.08294</v>
       </c>
     </row>
     <row r="42">
@@ -35334,7 +35334,7 @@
         <v>43405</v>
       </c>
       <c r="B42" t="n">
-        <v>3270224710.370745</v>
+        <v>3270224467.369715</v>
       </c>
     </row>
     <row r="43">
@@ -35342,7 +35342,7 @@
         <v>43435</v>
       </c>
       <c r="B43" t="n">
-        <v>2339058629.936319</v>
+        <v>2339058537.711595</v>
       </c>
     </row>
     <row r="44">
@@ -35350,7 +35350,7 @@
         <v>43466</v>
       </c>
       <c r="B44" t="n">
-        <v>2863801478.399277</v>
+        <v>2863801396.408808</v>
       </c>
     </row>
     <row r="45">
@@ -35358,7 +35358,7 @@
         <v>43497</v>
       </c>
       <c r="B45" t="n">
-        <v>2286165151.008707</v>
+        <v>2286165061.585979</v>
       </c>
     </row>
     <row r="46">
@@ -35366,7 +35366,7 @@
         <v>43525</v>
       </c>
       <c r="B46" t="n">
-        <v>2403666268.573534</v>
+        <v>2403666241.122518</v>
       </c>
     </row>
     <row r="47">
@@ -35374,7 +35374,7 @@
         <v>43556</v>
       </c>
       <c r="B47" t="n">
-        <v>2077829248.307001</v>
+        <v>2077829157.717659</v>
       </c>
     </row>
     <row r="48">
@@ -35382,7 +35382,7 @@
         <v>43586</v>
       </c>
       <c r="B48" t="n">
-        <v>2008990592.429118</v>
+        <v>2008990674.879247</v>
       </c>
     </row>
     <row r="49">
@@ -35390,7 +35390,7 @@
         <v>43617</v>
       </c>
       <c r="B49" t="n">
-        <v>1526350616.897392</v>
+        <v>1526350614.668512</v>
       </c>
     </row>
     <row r="50">
@@ -35398,7 +35398,7 @@
         <v>43647</v>
       </c>
       <c r="B50" t="n">
-        <v>1589365299.689857</v>
+        <v>1589365146.042911</v>
       </c>
     </row>
     <row r="51">
@@ -35406,7 +35406,7 @@
         <v>43678</v>
       </c>
       <c r="B51" t="n">
-        <v>1709685131.761247</v>
+        <v>1709685168.141712</v>
       </c>
     </row>
     <row r="52">
@@ -35414,7 +35414,7 @@
         <v>43709</v>
       </c>
       <c r="B52" t="n">
-        <v>1398975235.425663</v>
+        <v>1398975225.697899</v>
       </c>
     </row>
     <row r="53">
@@ -35422,7 +35422,7 @@
         <v>43739</v>
       </c>
       <c r="B53" t="n">
-        <v>1578080612.629849</v>
+        <v>1578080635.129348</v>
       </c>
     </row>
     <row r="54">
@@ -35430,7 +35430,7 @@
         <v>43770</v>
       </c>
       <c r="B54" t="n">
-        <v>1909638747.025585</v>
+        <v>1909638760.464764</v>
       </c>
     </row>
     <row r="55">
@@ -35438,7 +35438,7 @@
         <v>43800</v>
       </c>
       <c r="B55" t="n">
-        <v>1741241933.711097</v>
+        <v>1741241886.876606</v>
       </c>
     </row>
     <row r="56">
@@ -35446,7 +35446,7 @@
         <v>43831</v>
       </c>
       <c r="B56" t="n">
-        <v>1772561634.89923</v>
+        <v>1772561646.208264</v>
       </c>
     </row>
     <row r="57">
@@ -35454,7 +35454,7 @@
         <v>43862</v>
       </c>
       <c r="B57" t="n">
-        <v>4268220172.323026</v>
+        <v>4268220182.537079</v>
       </c>
     </row>
     <row r="58">
@@ -35462,7 +35462,7 @@
         <v>43891</v>
       </c>
       <c r="B58" t="n">
-        <v>4310317333.79416</v>
+        <v>4310317335.106243</v>
       </c>
     </row>
     <row r="59">
@@ -35470,7 +35470,7 @@
         <v>43922</v>
       </c>
       <c r="B59" t="n">
-        <v>3663569498.108727</v>
+        <v>3663569546.119599</v>
       </c>
     </row>
     <row r="60">
@@ -35478,7 +35478,7 @@
         <v>43952</v>
       </c>
       <c r="B60" t="n">
-        <v>5221682700.204563</v>
+        <v>5221682370.371246</v>
       </c>
     </row>
     <row r="61">
@@ -35486,7 +35486,7 @@
         <v>43983</v>
       </c>
       <c r="B61" t="n">
-        <v>4001159677.738016</v>
+        <v>4001159629.920266</v>
       </c>
     </row>
     <row r="62">
@@ -35494,7 +35494,7 @@
         <v>44013</v>
       </c>
       <c r="B62" t="n">
-        <v>3743314322.038477</v>
+        <v>3743314088.924234</v>
       </c>
     </row>
     <row r="63">
@@ -35502,7 +35502,7 @@
         <v>44044</v>
       </c>
       <c r="B63" t="n">
-        <v>5538476188.02116</v>
+        <v>5538476063.250587</v>
       </c>
     </row>
     <row r="64">
@@ -35510,7 +35510,7 @@
         <v>44075</v>
       </c>
       <c r="B64" t="n">
-        <v>9591019639.002119</v>
+        <v>9591020034.210024</v>
       </c>
     </row>
     <row r="65">
@@ -35518,7 +35518,7 @@
         <v>44105</v>
       </c>
       <c r="B65" t="n">
-        <v>4914765474.741329</v>
+        <v>4914765573.11873</v>
       </c>
     </row>
     <row r="66">
@@ -35526,7 +35526,7 @@
         <v>44136</v>
       </c>
       <c r="B66" t="n">
-        <v>5055653202.607536</v>
+        <v>5055653229.122925</v>
       </c>
     </row>
     <row r="67">
@@ -35534,7 +35534,7 @@
         <v>44166</v>
       </c>
       <c r="B67" t="n">
-        <v>3064971919.366837</v>
+        <v>3064972020.195354</v>
       </c>
     </row>
     <row r="68">
@@ -35542,7 +35542,7 @@
         <v>44197</v>
       </c>
       <c r="B68" t="n">
-        <v>4272179401.799252</v>
+        <v>4272179455.635673</v>
       </c>
     </row>
     <row r="69">
@@ -35550,7 +35550,7 @@
         <v>44228</v>
       </c>
       <c r="B69" t="n">
-        <v>4993958833.023874</v>
+        <v>4993958986.845518</v>
       </c>
     </row>
     <row r="70">
@@ -35558,7 +35558,7 @@
         <v>44256</v>
       </c>
       <c r="B70" t="n">
-        <v>4230832291.022425</v>
+        <v>4230832190.56005</v>
       </c>
     </row>
     <row r="71">
@@ -35566,7 +35566,7 @@
         <v>44287</v>
       </c>
       <c r="B71" t="n">
-        <v>4821919124.92625</v>
+        <v>4821919007.947468</v>
       </c>
     </row>
     <row r="72">
@@ -35574,7 +35574,7 @@
         <v>44317</v>
       </c>
       <c r="B72" t="n">
-        <v>5226246480.539894</v>
+        <v>5226246439.409256</v>
       </c>
     </row>
     <row r="73">
@@ -35582,7 +35582,7 @@
         <v>44348</v>
       </c>
       <c r="B73" t="n">
-        <v>8455848790.680625</v>
+        <v>8455848799.906297</v>
       </c>
     </row>
     <row r="74">
@@ -35590,7 +35590,7 @@
         <v>44378</v>
       </c>
       <c r="B74" t="n">
-        <v>7250314867.30067</v>
+        <v>7250315233.622869</v>
       </c>
     </row>
     <row r="75">
@@ -35598,7 +35598,7 @@
         <v>44409</v>
       </c>
       <c r="B75" t="n">
-        <v>6041826715.214469</v>
+        <v>6041826386.172901</v>
       </c>
     </row>
     <row r="76">
@@ -35606,7 +35606,7 @@
         <v>44440</v>
       </c>
       <c r="B76" t="n">
-        <v>5187963222.653525</v>
+        <v>5187963508.786974</v>
       </c>
     </row>
     <row r="77">
@@ -35614,7 +35614,7 @@
         <v>44470</v>
       </c>
       <c r="B77" t="n">
-        <v>5246803830.446607</v>
+        <v>5246804111.124493</v>
       </c>
     </row>
     <row r="78">
@@ -35622,7 +35622,7 @@
         <v>44501</v>
       </c>
       <c r="B78" t="n">
-        <v>15717939036.46941</v>
+        <v>15717939150.24885</v>
       </c>
     </row>
     <row r="79">
@@ -35630,7 +35630,7 @@
         <v>44531</v>
       </c>
       <c r="B79" t="n">
-        <v>14946670458.4856</v>
+        <v>14946669691.22011</v>
       </c>
     </row>
     <row r="80">
@@ -35638,7 +35638,7 @@
         <v>44562</v>
       </c>
       <c r="B80" t="n">
-        <v>13493538718.10045</v>
+        <v>13493538590.90481</v>
       </c>
     </row>
     <row r="81">
@@ -35646,7 +35646,7 @@
         <v>44593</v>
       </c>
       <c r="B81" t="n">
-        <v>13743048528.34902</v>
+        <v>13743048357.92401</v>
       </c>
     </row>
     <row r="82">
@@ -35654,7 +35654,7 @@
         <v>44621</v>
       </c>
       <c r="B82" t="n">
-        <v>12664921561.98137</v>
+        <v>12664921353.59582</v>
       </c>
     </row>
     <row r="83">
@@ -35662,7 +35662,7 @@
         <v>44652</v>
       </c>
       <c r="B83" t="n">
-        <v>12069929311.44285</v>
+        <v>12069929531.71988</v>
       </c>
     </row>
     <row r="84">
@@ -35670,7 +35670,7 @@
         <v>44682</v>
       </c>
       <c r="B84" t="n">
-        <v>11649542571.27498</v>
+        <v>11649542739.25881</v>
       </c>
     </row>
     <row r="85">
@@ -35678,7 +35678,7 @@
         <v>44713</v>
       </c>
       <c r="B85" t="n">
-        <v>8489482564.836275</v>
+        <v>8489482874.203092</v>
       </c>
     </row>
     <row r="86">
@@ -35686,7 +35686,7 @@
         <v>44743</v>
       </c>
       <c r="B86" t="n">
-        <v>8610809762.630081</v>
+        <v>8610809537.190723</v>
       </c>
     </row>
     <row r="87">
@@ -35694,7 +35694,7 @@
         <v>44774</v>
       </c>
       <c r="B87" t="n">
-        <v>9233110416.166264</v>
+        <v>9233110943.686735</v>
       </c>
     </row>
     <row r="88">
@@ -35702,7 +35702,7 @@
         <v>44805</v>
       </c>
       <c r="B88" t="n">
-        <v>8220308153.778984</v>
+        <v>8220307964.633487</v>
       </c>
     </row>
     <row r="89">
@@ -35710,7 +35710,7 @@
         <v>44835</v>
       </c>
       <c r="B89" t="n">
-        <v>7390135201.267742</v>
+        <v>7390134873.710088</v>
       </c>
     </row>
     <row r="90">
@@ -35718,7 +35718,7 @@
         <v>44866</v>
       </c>
       <c r="B90" t="n">
-        <v>7689883999.936604</v>
+        <v>7689883749.582563</v>
       </c>
     </row>
     <row r="91">
@@ -35726,7 +35726,7 @@
         <v>44896</v>
       </c>
       <c r="B91" t="n">
-        <v>6933557906.997817</v>
+        <v>6933557571.203413</v>
       </c>
     </row>
     <row r="92">
@@ -35734,7 +35734,7 @@
         <v>44927</v>
       </c>
       <c r="B92" t="n">
-        <v>8221944933.383608</v>
+        <v>8221944728.960037</v>
       </c>
     </row>
     <row r="93">
@@ -35742,7 +35742,7 @@
         <v>44958</v>
       </c>
       <c r="B93" t="n">
-        <v>12078125537.09773</v>
+        <v>12078125594.63622</v>
       </c>
     </row>
     <row r="94">
@@ -35750,7 +35750,7 @@
         <v>44986</v>
       </c>
       <c r="B94" t="n">
-        <v>12270776489.82504</v>
+        <v>12270776759.34808</v>
       </c>
     </row>
     <row r="95">
@@ -35758,7 +35758,7 @@
         <v>45017</v>
       </c>
       <c r="B95" t="n">
-        <v>10592547114.8512</v>
+        <v>10592546983.15068</v>
       </c>
     </row>
     <row r="96">
@@ -35766,7 +35766,7 @@
         <v>45047</v>
       </c>
       <c r="B96" t="n">
-        <v>17384080881.73069</v>
+        <v>17384081108.25114</v>
       </c>
     </row>
     <row r="97">
@@ -35774,7 +35774,7 @@
         <v>45078</v>
       </c>
       <c r="B97" t="n">
-        <v>20510416229.61734</v>
+        <v>20510416617.15553</v>
       </c>
     </row>
     <row r="98">
@@ -35782,7 +35782,7 @@
         <v>45108</v>
       </c>
       <c r="B98" t="n">
-        <v>19516665404.41132</v>
+        <v>19516666394.23046</v>
       </c>
     </row>
     <row r="99">
@@ -35790,7 +35790,7 @@
         <v>45139</v>
       </c>
       <c r="B99" t="n">
-        <v>26892085442.28114</v>
+        <v>26892085282.89082</v>
       </c>
     </row>
     <row r="100">
@@ -35798,7 +35798,7 @@
         <v>45170</v>
       </c>
       <c r="B100" t="n">
-        <v>18956786193.91842</v>
+        <v>18956786256.3139</v>
       </c>
     </row>
     <row r="101">
@@ -35806,7 +35806,7 @@
         <v>45200</v>
       </c>
       <c r="B101" t="n">
-        <v>20004110614.40416</v>
+        <v>20004110873.25478</v>
       </c>
     </row>
     <row r="102">
@@ -35814,7 +35814,7 @@
         <v>45231</v>
       </c>
       <c r="B102" t="n">
-        <v>20662350586.79599</v>
+        <v>20662350889.41992</v>
       </c>
     </row>
     <row r="103">
@@ -35822,7 +35822,7 @@
         <v>45261</v>
       </c>
       <c r="B103" t="n">
-        <v>17729040238.73692</v>
+        <v>17729040188.06858</v>
       </c>
     </row>
     <row r="104">
@@ -35830,7 +35830,7 @@
         <v>45292</v>
       </c>
       <c r="B104" t="n">
-        <v>25939419774.41552</v>
+        <v>25939419759.39923</v>
       </c>
     </row>
     <row r="105">
@@ -35838,7 +35838,7 @@
         <v>45323</v>
       </c>
       <c r="B105" t="n">
-        <v>40100316620.61958</v>
+        <v>40100317471.08879</v>
       </c>
     </row>
     <row r="106">
@@ -35846,7 +35846,7 @@
         <v>45352</v>
       </c>
       <c r="B106" t="n">
-        <v>54116072750.16327</v>
+        <v>54116072605.90096</v>
       </c>
     </row>
     <row r="107">
@@ -35854,7 +35854,7 @@
         <v>45383</v>
       </c>
       <c r="B107" t="n">
-        <v>38842930826.68027</v>
+        <v>38842932353.45078</v>
       </c>
     </row>
     <row r="108">
@@ -35862,7 +35862,7 @@
         <v>45413</v>
       </c>
       <c r="B108" t="n">
-        <v>42766666588.00021</v>
+        <v>42766667754.27766</v>
       </c>
     </row>
     <row r="109">
@@ -35870,7 +35870,7 @@
         <v>45444</v>
       </c>
       <c r="B109" t="n">
-        <v>48378555652.19691</v>
+        <v>48378555897.5914</v>
       </c>
     </row>
     <row r="110">
@@ -35878,7 +35878,7 @@
         <v>45474</v>
       </c>
       <c r="B110" t="n">
-        <v>35004278111.62473</v>
+        <v>35004278763.2421</v>
       </c>
     </row>
     <row r="111">
@@ -35886,7 +35886,7 @@
         <v>45505</v>
       </c>
       <c r="B111" t="n">
-        <v>42578841798.59255</v>
+        <v>42578842389.77814</v>
       </c>
     </row>
     <row r="112">
@@ -35894,7 +35894,7 @@
         <v>45536</v>
       </c>
       <c r="B112" t="n">
-        <v>35817074857.85065</v>
+        <v>35817076481.33392</v>
       </c>
     </row>
     <row r="113">
@@ -35902,7 +35902,7 @@
         <v>45566</v>
       </c>
       <c r="B113" t="n">
-        <v>32600566148.4255</v>
+        <v>32600565649.69154</v>
       </c>
     </row>
     <row r="114">
@@ -35910,7 +35910,7 @@
         <v>45597</v>
       </c>
       <c r="B114" t="n">
-        <v>31985011735.90187</v>
+        <v>31985012267.4627</v>
       </c>
     </row>
     <row r="115">
@@ -35918,7 +35918,7 @@
         <v>45627</v>
       </c>
       <c r="B115" t="n">
-        <v>26515688268.10477</v>
+        <v>26515687818.22706</v>
       </c>
     </row>
     <row r="116">
@@ -35926,7 +35926,7 @@
         <v>45658</v>
       </c>
       <c r="B116" t="n">
-        <v>39289486358.55137</v>
+        <v>39289486511.36562</v>
       </c>
     </row>
     <row r="117">
@@ -35934,7 +35934,7 @@
         <v>45689</v>
       </c>
       <c r="B117" t="n">
-        <v>32133024139.17048</v>
+        <v>32133024447.99046</v>
       </c>
     </row>
     <row r="118">
@@ -35942,7 +35942,7 @@
         <v>45717</v>
       </c>
       <c r="B118" t="n">
-        <v>33609223033.66285</v>
+        <v>33609222854.53938</v>
       </c>
     </row>
     <row r="119">
@@ -35950,7 +35950,7 @@
         <v>45748</v>
       </c>
       <c r="B119" t="n">
-        <v>33845541376.64889</v>
+        <v>33845541809.23596</v>
       </c>
     </row>
     <row r="120">
@@ -35958,7 +35958,7 @@
         <v>45778</v>
       </c>
       <c r="B120" t="n">
-        <v>29082742301.91574</v>
+        <v>29082741672.72074</v>
       </c>
     </row>
     <row r="121">
@@ -35966,7 +35966,7 @@
         <v>45809</v>
       </c>
       <c r="B121" t="n">
-        <v>27853410382.11868</v>
+        <v>27853411119.15093</v>
       </c>
     </row>
     <row r="122">
@@ -35974,7 +35974,7 @@
         <v>45839</v>
       </c>
       <c r="B122" t="n">
-        <v>27389922873.85192</v>
+        <v>27389921193.10247</v>
       </c>
     </row>
     <row r="123">
@@ -35982,7 +35982,7 @@
         <v>45870</v>
       </c>
       <c r="B123" t="n">
-        <v>30709050730.9651</v>
+        <v>30709051255.2948</v>
       </c>
     </row>
     <row r="124">
@@ -35990,7 +35990,7 @@
         <v>45901</v>
       </c>
       <c r="B124" t="n">
-        <v>32524643561.45914</v>
+        <v>32524643145.8273</v>
       </c>
     </row>
     <row r="125">
@@ -35998,7 +35998,7 @@
         <v>45931</v>
       </c>
       <c r="B125" t="n">
-        <v>33105939647.43792</v>
+        <v>33105939936.52052</v>
       </c>
     </row>
     <row r="126">
@@ -36006,7 +36006,7 @@
         <v>45962</v>
       </c>
       <c r="B126" t="n">
-        <v>40842151404.3355</v>
+        <v>40842150158.30857</v>
       </c>
     </row>
     <row r="127">
@@ -36014,7 +36014,7 @@
         <v>45992</v>
       </c>
       <c r="B127" t="n">
-        <v>29884818995.19355</v>
+        <v>29884819259.77242</v>
       </c>
     </row>
     <row r="128">
@@ -36022,7 +36022,7 @@
         <v>46023</v>
       </c>
       <c r="B128" t="n">
-        <v>30639420819.37004</v>
+        <v>30639420705.97175</v>
       </c>
     </row>
     <row r="129">
@@ -36030,7 +36030,7 @@
         <v>46054</v>
       </c>
       <c r="B129" t="n">
-        <v>36431005418.7243</v>
+        <v>36431005459.34392</v>
       </c>
     </row>
     <row r="130">
@@ -36038,7 +36038,7 @@
         <v>46082</v>
       </c>
       <c r="B130" t="n">
-        <v>32571482558.46391</v>
+        <v>32571482282.69625</v>
       </c>
     </row>
     <row r="131">
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.260799340882456e-43</v>
+        <v>2.260798596609114e-43</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -36274,7 +36274,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.790696702479751e-18</v>
+        <v>2.790695313710477e-18</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>

--- a/006/xy_006_data.xlsx
+++ b/006/xy_006_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Attention Is All You Trade</t>
+          <t>Attention Is All You Trade, Briefly</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The more people read about Nvidia, the more dollars change hands.</t>
+          <t>The more people read about Nvidia, the more of its shares change hands.</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Attention and trading volume move together, with diminishing returns.</t>
+          <t>Attention spikes bring trading spikes, not a lasting trading boom.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:04</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NVDA dollar volume ($/day, avg)</t>
+          <t>NVDA shares traded (per day, avg)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NVDA daily dollar volume (close x shares traded), averaged by month, Yahoo Finance, 07/2015 - 08/2026</t>
+          <t>NVDA shares traded per day, split-adjusted, averaged by month, Yahoo Finance, 07/2015 - present</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:04</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C136"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>NVDA dollar volume ($/day, avg)</t>
+          <t>NVDA shares traded (per day, avg)</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
         <v>1298.225806451613</v>
       </c>
       <c r="C2" t="n">
-        <v>119176737.0071465</v>
+        <v>249109272.7272727</v>
       </c>
     </row>
     <row r="3">
@@ -835,7 +835,7 @@
         <v>1282.677419354839</v>
       </c>
       <c r="C3" t="n">
-        <v>241792640.3872172</v>
+        <v>450928190.4761904</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +846,7 @@
         <v>1271.966666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>172128030.513173</v>
+        <v>308581333.3333333</v>
       </c>
     </row>
     <row r="5">
@@ -857,7 +857,7 @@
         <v>1384.41935483871</v>
       </c>
       <c r="C5" t="n">
-        <v>238658506.1465502</v>
+        <v>366014363.6363636</v>
       </c>
     </row>
     <row r="6">
@@ -868,7 +868,7 @@
         <v>1533.233333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>271074534.4281673</v>
+        <v>367240800</v>
       </c>
     </row>
     <row r="7">
@@ -879,7 +879,7 @@
         <v>1406.451612903226</v>
       </c>
       <c r="C7" t="n">
-        <v>204999180.6225777</v>
+        <v>255780545.4545455</v>
       </c>
     </row>
     <row r="8">
@@ -890,7 +890,7 @@
         <v>1532.935483870968</v>
       </c>
       <c r="C8" t="n">
-        <v>304536300.5475119</v>
+        <v>428367368.4210526</v>
       </c>
     </row>
     <row r="9">
@@ -901,7 +901,7 @@
         <v>1478.51724137931</v>
       </c>
       <c r="C9" t="n">
-        <v>312717808.2038879</v>
+        <v>450002400</v>
       </c>
     </row>
     <row r="10">
@@ -912,7 +912,7 @@
         <v>1448.258064516129</v>
       </c>
       <c r="C10" t="n">
-        <v>244389643.8930793</v>
+        <v>298995636.3636364</v>
       </c>
     </row>
     <row r="11">
@@ -923,7 +923,7 @@
         <v>1506.533333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>283940229.4481141</v>
+        <v>320678666.6666667</v>
       </c>
     </row>
     <row r="12">
@@ -934,7 +934,7 @@
         <v>1962.709677419355</v>
       </c>
       <c r="C12" t="n">
-        <v>493459851.9519965</v>
+        <v>493706476.1904762</v>
       </c>
     </row>
     <row r="13">
@@ -945,7 +945,7 @@
         <v>1586.166666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>425646461.7016532</v>
+        <v>372631818.1818182</v>
       </c>
     </row>
     <row r="14">
@@ -956,7 +956,7 @@
         <v>1516.129032258065</v>
       </c>
       <c r="C14" t="n">
-        <v>467127451.218462</v>
+        <v>360502600</v>
       </c>
     </row>
     <row r="15">
@@ -967,7 +967,7 @@
         <v>1529.225806451613</v>
       </c>
       <c r="C15" t="n">
-        <v>602732021.942968</v>
+        <v>404570434.7826087</v>
       </c>
     </row>
     <row r="16">
@@ -978,7 +978,7 @@
         <v>1532.1</v>
       </c>
       <c r="C16" t="n">
-        <v>640112893.6097054</v>
+        <v>412631047.6190476</v>
       </c>
     </row>
     <row r="17">
@@ -989,7 +989,7 @@
         <v>1627.064516129032</v>
       </c>
       <c r="C17" t="n">
-        <v>522120957.7855837</v>
+        <v>311979428.5714286</v>
       </c>
     </row>
     <row r="18">
@@ -1000,7 +1000,7 @@
         <v>1879.366666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>1252364820.939087</v>
+        <v>607974476.1904762</v>
       </c>
     </row>
     <row r="19">
@@ -1011,7 +1011,7 @@
         <v>1939.935483870968</v>
       </c>
       <c r="C19" t="n">
-        <v>2170773464.907056</v>
+        <v>861058476.1904762</v>
       </c>
     </row>
     <row r="20">
@@ -1022,7 +1022,7 @@
         <v>2127.193548387097</v>
       </c>
       <c r="C20" t="n">
-        <v>1727593753.759003</v>
+        <v>669842000</v>
       </c>
     </row>
     <row r="21">
@@ -1033,7 +1033,7 @@
         <v>2087.678571428572</v>
       </c>
       <c r="C21" t="n">
-        <v>2012906071.050644</v>
+        <v>747725684.2105263</v>
       </c>
     </row>
     <row r="22">
@@ -1044,7 +1044,7 @@
         <v>1859.483870967742</v>
       </c>
       <c r="C22" t="n">
-        <v>1582464114.376856</v>
+        <v>621259130.4347826</v>
       </c>
     </row>
     <row r="23">
@@ -1055,7 +1055,7 @@
         <v>1512.6</v>
       </c>
       <c r="C23" t="n">
-        <v>1248475607.773781</v>
+        <v>503819578.9473684</v>
       </c>
     </row>
     <row r="24">
@@ -1066,7 +1066,7 @@
         <v>2128.709677419355</v>
       </c>
       <c r="C24" t="n">
-        <v>2766373599.863963</v>
+        <v>873156545.4545455</v>
       </c>
     </row>
     <row r="25">
@@ -1077,7 +1077,7 @@
         <v>1973.733333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>3969353568.35647</v>
+        <v>1065705454.545455</v>
       </c>
     </row>
     <row r="26">
@@ -1088,7 +1088,7 @@
         <v>1766.677419354839</v>
       </c>
       <c r="C26" t="n">
-        <v>3037885000.704908</v>
+        <v>774550800</v>
       </c>
     </row>
     <row r="27">
@@ -1099,7 +1099,7 @@
         <v>1769.903225806452</v>
       </c>
       <c r="C27" t="n">
-        <v>2603482797.420419</v>
+        <v>640357217.3913044</v>
       </c>
     </row>
     <row r="28">
@@ -1110,7 +1110,7 @@
         <v>1888.633333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>3139738921.092033</v>
+        <v>722366800</v>
       </c>
     </row>
     <row r="29">
@@ -1121,7 +1121,7 @@
         <v>2391.677419354839</v>
       </c>
       <c r="C29" t="n">
-        <v>2467356088.232561</v>
+        <v>519212000</v>
       </c>
     </row>
     <row r="30">
@@ -1132,7 +1132,7 @@
         <v>2574.466666666667</v>
       </c>
       <c r="C30" t="n">
-        <v>2902427293.988728</v>
+        <v>563376000</v>
       </c>
     </row>
     <row r="31">
@@ -1143,7 +1143,7 @@
         <v>2166.709677419355</v>
       </c>
       <c r="C31" t="n">
-        <v>2395161410.512543</v>
+        <v>505610800</v>
       </c>
     </row>
     <row r="32">
@@ -1154,7 +1154,7 @@
         <v>2707.193548387097</v>
       </c>
       <c r="C32" t="n">
-        <v>3053681058.660235</v>
+        <v>545534095.2380953</v>
       </c>
     </row>
     <row r="33">
@@ -1165,7 +1165,7 @@
         <v>2507.035714285714</v>
       </c>
       <c r="C33" t="n">
-        <v>4529898829.469781</v>
+        <v>785027789.4736842</v>
       </c>
     </row>
     <row r="34">
@@ -1176,7 +1176,7 @@
         <v>2316.129032258064</v>
       </c>
       <c r="C34" t="n">
-        <v>3955656275.772549</v>
+        <v>672306666.6666666</v>
       </c>
     </row>
     <row r="35">
@@ -1187,7 +1187,7 @@
         <v>1928.9</v>
       </c>
       <c r="C35" t="n">
-        <v>2951766859.723591</v>
+        <v>530667047.6190476</v>
       </c>
     </row>
     <row r="36">
@@ -1198,7 +1198,7 @@
         <v>1936.516129032258</v>
       </c>
       <c r="C36" t="n">
-        <v>3336711199.892044</v>
+        <v>544465454.5454545</v>
       </c>
     </row>
     <row r="37">
@@ -1209,7 +1209,7 @@
         <v>1850.633333333333</v>
       </c>
       <c r="C37" t="n">
-        <v>2643527824.292228</v>
+        <v>418359047.6190476</v>
       </c>
     </row>
     <row r="38">
@@ -1220,7 +1220,7 @@
         <v>1745.838709677419</v>
       </c>
       <c r="C38" t="n">
-        <v>1849653192.506699</v>
+        <v>301041714.2857143</v>
       </c>
     </row>
     <row r="39">
@@ -1231,7 +1231,7 @@
         <v>2394</v>
       </c>
       <c r="C39" t="n">
-        <v>3048666656.494804</v>
+        <v>474688521.7391304</v>
       </c>
     </row>
     <row r="40">
@@ -1242,7 +1242,7 @@
         <v>1712.233333333333</v>
       </c>
       <c r="C40" t="n">
-        <v>2246803847.557971</v>
+        <v>333694736.8421053</v>
       </c>
     </row>
     <row r="41">
@@ -1253,7 +1253,7 @@
         <v>1700.193548387097</v>
       </c>
       <c r="C41" t="n">
-        <v>3244947761.08294</v>
+        <v>564259826.0869565</v>
       </c>
     </row>
     <row r="42">
@@ -1264,7 +1264,7 @@
         <v>1865.533333333333</v>
       </c>
       <c r="C42" t="n">
-        <v>3270224467.369715</v>
+        <v>769635238.0952381</v>
       </c>
     </row>
     <row r="43">
@@ -1275,7 +1275,7 @@
         <v>1616.032258064516</v>
       </c>
       <c r="C43" t="n">
-        <v>2339058537.711595</v>
+        <v>655337263.1578947</v>
       </c>
     </row>
     <row r="44">
@@ -1286,7 +1286,7 @@
         <v>2007.225806451613</v>
       </c>
       <c r="C44" t="n">
-        <v>2863801396.408808</v>
+        <v>803380571.4285715</v>
       </c>
     </row>
     <row r="45">
@@ -1297,7 +1297,7 @@
         <v>1693.642857142857</v>
       </c>
       <c r="C45" t="n">
-        <v>2286165061.585979</v>
+        <v>602406736.8421053</v>
       </c>
     </row>
     <row r="46">
@@ -1308,7 +1308,7 @@
         <v>1730.290322580645</v>
       </c>
       <c r="C46" t="n">
-        <v>2403666241.122518</v>
+        <v>574692380.9523809</v>
       </c>
     </row>
     <row r="47">
@@ -1319,7 +1319,7 @@
         <v>1457.6</v>
       </c>
       <c r="C47" t="n">
-        <v>2077829157.717659</v>
+        <v>449418095.2380952</v>
       </c>
     </row>
     <row r="48">
@@ -1330,7 +1330,7 @@
         <v>1557.741935483871</v>
       </c>
       <c r="C48" t="n">
-        <v>2008990674.879247</v>
+        <v>508216000</v>
       </c>
     </row>
     <row r="49">
@@ -1341,7 +1341,7 @@
         <v>1509.8</v>
       </c>
       <c r="C49" t="n">
-        <v>1526350614.668512</v>
+        <v>411667000</v>
       </c>
     </row>
     <row r="50">
@@ -1352,7 +1352,7 @@
         <v>1570.129032258065</v>
       </c>
       <c r="C50" t="n">
-        <v>1589365146.042911</v>
+        <v>382544727.2727273</v>
       </c>
     </row>
     <row r="51">
@@ -1363,7 +1363,7 @@
         <v>1545.516129032258</v>
       </c>
       <c r="C51" t="n">
-        <v>1709685168.141712</v>
+        <v>429560363.6363636</v>
       </c>
     </row>
     <row r="52">
@@ -1374,7 +1374,7 @@
         <v>1475.533333333333</v>
       </c>
       <c r="C52" t="n">
-        <v>1398975225.697899</v>
+        <v>317388400</v>
       </c>
     </row>
     <row r="53">
@@ -1385,7 +1385,7 @@
         <v>1672.225806451613</v>
       </c>
       <c r="C53" t="n">
-        <v>1578080635.129348</v>
+        <v>334616173.9130435</v>
       </c>
     </row>
     <row r="54">
@@ -1396,7 +1396,7 @@
         <v>1982.8</v>
       </c>
       <c r="C54" t="n">
-        <v>1909638760.464764</v>
+        <v>366090000</v>
       </c>
     </row>
     <row r="55">
@@ -1407,7 +1407,7 @@
         <v>1901.58064516129</v>
       </c>
       <c r="C55" t="n">
-        <v>1741241886.876606</v>
+        <v>311596761.9047619</v>
       </c>
     </row>
     <row r="56">
@@ -1418,7 +1418,7 @@
         <v>1939.709677419355</v>
       </c>
       <c r="C56" t="n">
-        <v>1772561646.208264</v>
+        <v>291686285.7142857</v>
       </c>
     </row>
     <row r="57">
@@ -1429,7 +1429,7 @@
         <v>2214.655172413793</v>
       </c>
       <c r="C57" t="n">
-        <v>4268220182.537079</v>
+        <v>623613263.1578947</v>
       </c>
     </row>
     <row r="58">
@@ -1440,7 +1440,7 @@
         <v>1884.709677419355</v>
       </c>
       <c r="C58" t="n">
-        <v>4310317335.106243</v>
+        <v>716997818.1818181</v>
       </c>
     </row>
     <row r="59">
@@ -1451,7 +1451,7 @@
         <v>2553.6</v>
       </c>
       <c r="C59" t="n">
-        <v>3663569546.119599</v>
+        <v>537062095.2380953</v>
       </c>
     </row>
     <row r="60">
@@ -1462,7 +1462,7 @@
         <v>2908.16129032258</v>
       </c>
       <c r="C60" t="n">
-        <v>5221682370.371246</v>
+        <v>627443800</v>
       </c>
     </row>
     <row r="61">
@@ -1473,7 +1473,7 @@
         <v>2159.2</v>
       </c>
       <c r="C61" t="n">
-        <v>4001159629.920266</v>
+        <v>441793818.1818182</v>
       </c>
     </row>
     <row r="62">
@@ -1484,7 +1484,7 @@
         <v>2442.258064516129</v>
       </c>
       <c r="C62" t="n">
-        <v>3743314088.924234</v>
+        <v>367929636.3636364</v>
       </c>
     </row>
     <row r="63">
@@ -1495,7 +1495,7 @@
         <v>2704.741935483871</v>
       </c>
       <c r="C63" t="n">
-        <v>5538476063.250587</v>
+        <v>460597333.3333333</v>
       </c>
     </row>
     <row r="64">
@@ -1506,7 +1506,7 @@
         <v>6176.033333333334</v>
       </c>
       <c r="C64" t="n">
-        <v>9591020034.210024</v>
+        <v>755073904.7619047</v>
       </c>
     </row>
     <row r="65">
@@ -1517,7 +1517,7 @@
         <v>2910.16129032258</v>
       </c>
       <c r="C65" t="n">
-        <v>4914765573.11873</v>
+        <v>364652545.4545454</v>
       </c>
     </row>
     <row r="66">
@@ -1528,7 +1528,7 @@
         <v>2748.8</v>
       </c>
       <c r="C66" t="n">
-        <v>5055653229.122925</v>
+        <v>379741000</v>
       </c>
     </row>
     <row r="67">
@@ -1539,7 +1539,7 @@
         <v>2842.096774193548</v>
       </c>
       <c r="C67" t="n">
-        <v>3064972020.195354</v>
+        <v>232772545.4545455</v>
       </c>
     </row>
     <row r="68">
@@ -1550,7 +1550,7 @@
         <v>2434.225806451613</v>
       </c>
       <c r="C68" t="n">
-        <v>4272179455.635673</v>
+        <v>323903789.4736842</v>
       </c>
     </row>
     <row r="69">
@@ -1561,7 +1561,7 @@
         <v>2552.964285714286</v>
       </c>
       <c r="C69" t="n">
-        <v>4993958986.845518</v>
+        <v>351596000</v>
       </c>
     </row>
     <row r="70">
@@ -1572,7 +1572,7 @@
         <v>2229.58064516129</v>
       </c>
       <c r="C70" t="n">
-        <v>4230832190.56005</v>
+        <v>332550260.8695652</v>
       </c>
     </row>
     <row r="71">
@@ -1583,7 +1583,7 @@
         <v>2665.766666666667</v>
       </c>
       <c r="C71" t="n">
-        <v>4821919007.947468</v>
+        <v>319942666.6666667</v>
       </c>
     </row>
     <row r="72">
@@ -1594,7 +1594,7 @@
         <v>1874.451612903226</v>
       </c>
       <c r="C72" t="n">
-        <v>5226246439.409256</v>
+        <v>352719000</v>
       </c>
     </row>
     <row r="73">
@@ -1605,7 +1605,7 @@
         <v>2106.2</v>
       </c>
       <c r="C73" t="n">
-        <v>8455848799.906297</v>
+        <v>466967818.1818182</v>
       </c>
     </row>
     <row r="74">
@@ -1616,7 +1616,7 @@
         <v>3009.967741935484</v>
       </c>
       <c r="C74" t="n">
-        <v>7250315233.622869</v>
+        <v>372527476.1904762</v>
       </c>
     </row>
     <row r="75">
@@ -1627,7 +1627,7 @@
         <v>2687.83870967742</v>
       </c>
       <c r="C75" t="n">
-        <v>6041826386.172901</v>
+        <v>291653909.0909091</v>
       </c>
     </row>
     <row r="76">
@@ -1638,7 +1638,7 @@
         <v>2291.7</v>
       </c>
       <c r="C76" t="n">
-        <v>5187963508.786974</v>
+        <v>238046952.3809524</v>
       </c>
     </row>
     <row r="77">
@@ -1649,7 +1649,7 @@
         <v>2480</v>
       </c>
       <c r="C77" t="n">
-        <v>5246804111.124493</v>
+        <v>236718000</v>
       </c>
     </row>
     <row r="78">
@@ -1660,7 +1660,7 @@
         <v>3524.033333333333</v>
       </c>
       <c r="C78" t="n">
-        <v>15717939150.24885</v>
+        <v>514817619.047619</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         <v>2796.483870967742</v>
       </c>
       <c r="C79" t="n">
-        <v>14946669691.22011</v>
+        <v>502659318.1818182</v>
       </c>
     </row>
     <row r="80">
@@ -1682,7 +1682,7 @@
         <v>3098.774193548387</v>
       </c>
       <c r="C80" t="n">
-        <v>13493538590.90481</v>
+        <v>534108200</v>
       </c>
     </row>
     <row r="81">
@@ -1693,7 +1693,7 @@
         <v>3629</v>
       </c>
       <c r="C81" t="n">
-        <v>13743048357.92401</v>
+        <v>560224736.8421053</v>
       </c>
     </row>
     <row r="82">
@@ -1704,7 +1704,7 @@
         <v>2717.83870967742</v>
       </c>
       <c r="C82" t="n">
-        <v>12664921353.59582</v>
+        <v>506286913.0434783</v>
       </c>
     </row>
     <row r="83">
@@ -1715,7 +1715,7 @@
         <v>2543.733333333333</v>
       </c>
       <c r="C83" t="n">
-        <v>12069929531.71988</v>
+        <v>555719500</v>
       </c>
     </row>
     <row r="84">
@@ -1726,7 +1726,7 @@
         <v>2563.741935483871</v>
       </c>
       <c r="C84" t="n">
-        <v>11649542739.25881</v>
+        <v>658715285.7142857</v>
       </c>
     </row>
     <row r="85">
@@ -1737,7 +1737,7 @@
         <v>2212.2</v>
       </c>
       <c r="C85" t="n">
-        <v>8489482874.203092</v>
+        <v>502609095.2380952</v>
       </c>
     </row>
     <row r="86">
@@ -1748,7 +1748,7 @@
         <v>2478.870967741936</v>
       </c>
       <c r="C86" t="n">
-        <v>8610809537.190723</v>
+        <v>528223800</v>
       </c>
     </row>
     <row r="87">
@@ -1759,7 +1759,7 @@
         <v>2578.41935483871</v>
       </c>
       <c r="C87" t="n">
-        <v>9233110943.686735</v>
+        <v>524767304.3478261</v>
       </c>
     </row>
     <row r="88">
@@ -1770,7 +1770,7 @@
         <v>3461.933333333333</v>
       </c>
       <c r="C88" t="n">
-        <v>8220307964.633487</v>
+        <v>625265619.0476191</v>
       </c>
     </row>
     <row r="89">
@@ -1781,7 +1781,7 @@
         <v>2781.032258064516</v>
       </c>
       <c r="C89" t="n">
-        <v>7390134873.710088</v>
+        <v>597584619.0476191</v>
       </c>
     </row>
     <row r="90">
@@ -1792,7 +1792,7 @@
         <v>2871.766666666667</v>
       </c>
       <c r="C90" t="n">
-        <v>7689883749.582563</v>
+        <v>504790619.047619</v>
       </c>
     </row>
     <row r="91">
@@ -1803,7 +1803,7 @@
         <v>2108.83870967742</v>
       </c>
       <c r="C91" t="n">
-        <v>6933557571.203413</v>
+        <v>426007238.0952381</v>
       </c>
     </row>
     <row r="92">
@@ -1814,7 +1814,7 @@
         <v>2195.83870967742</v>
       </c>
       <c r="C92" t="n">
-        <v>8221944728.960037</v>
+        <v>472748000</v>
       </c>
     </row>
     <row r="93">
@@ -1825,7 +1825,7 @@
         <v>2518.964285714286</v>
       </c>
       <c r="C93" t="n">
-        <v>12078125594.63622</v>
+        <v>547025210.5263158</v>
       </c>
     </row>
     <row r="94">
@@ -1836,7 +1836,7 @@
         <v>3074.193548387097</v>
       </c>
       <c r="C94" t="n">
-        <v>12270776759.34808</v>
+        <v>489727434.7826087</v>
       </c>
     </row>
     <row r="95">
@@ -1847,7 +1847,7 @@
         <v>2653.633333333333</v>
       </c>
       <c r="C95" t="n">
-        <v>10592546983.15068</v>
+        <v>391392105.2631579</v>
       </c>
     </row>
     <row r="96">
@@ -1858,7 +1858,7 @@
         <v>7040.548387096775</v>
       </c>
       <c r="C96" t="n">
-        <v>17384081108.25114</v>
+        <v>531719045.4545454</v>
       </c>
     </row>
     <row r="97">
@@ -1869,7 +1869,7 @@
         <v>5477</v>
       </c>
       <c r="C97" t="n">
-        <v>20510416617.15553</v>
+        <v>501288095.2380952</v>
       </c>
     </row>
     <row r="98">
@@ -1880,7 +1880,7 @@
         <v>3981.806451612903</v>
       </c>
       <c r="C98" t="n">
-        <v>19516666394.23046</v>
+        <v>435342250</v>
       </c>
     </row>
     <row r="99">
@@ -1891,7 +1891,7 @@
         <v>5717.967741935484</v>
       </c>
       <c r="C99" t="n">
-        <v>26892085282.89082</v>
+        <v>592702260.8695652</v>
       </c>
     </row>
     <row r="100">
@@ -1902,7 +1902,7 @@
         <v>5511</v>
       </c>
       <c r="C100" t="n">
-        <v>18956786256.3139</v>
+        <v>428963650</v>
       </c>
     </row>
     <row r="101">
@@ -1913,7 +1913,7 @@
         <v>4307.548387096775</v>
       </c>
       <c r="C101" t="n">
-        <v>20004110873.25478</v>
+        <v>460959136.3636364</v>
       </c>
     </row>
     <row r="102">
@@ -1924,7 +1924,7 @@
         <v>4725.066666666667</v>
       </c>
       <c r="C102" t="n">
-        <v>20662350889.41992</v>
+        <v>435458000</v>
       </c>
     </row>
     <row r="103">
@@ -1935,7 +1935,7 @@
         <v>5359.677419354839</v>
       </c>
       <c r="C103" t="n">
-        <v>17729040188.06858</v>
+        <v>370594350</v>
       </c>
     </row>
     <row r="104">
@@ -1946,7 +1946,7 @@
         <v>6081.290322580645</v>
       </c>
       <c r="C104" t="n">
-        <v>25939419759.39923</v>
+        <v>462201761.9047619</v>
       </c>
     </row>
     <row r="105">
@@ -1957,7 +1957,7 @@
         <v>16719.93103448276</v>
       </c>
       <c r="C105" t="n">
-        <v>40100317471.08879</v>
+        <v>553067800</v>
       </c>
     </row>
     <row r="106">
@@ -1968,7 +1968,7 @@
         <v>11840.38709677419</v>
       </c>
       <c r="C106" t="n">
-        <v>54116072605.90096</v>
+        <v>607460900</v>
       </c>
     </row>
     <row r="107">
@@ -1979,7 +1979,7 @@
         <v>6815</v>
       </c>
       <c r="C107" t="n">
-        <v>38842932353.45078</v>
+        <v>457833363.6363636</v>
       </c>
     </row>
     <row r="108">
@@ -1990,7 +1990,7 @@
         <v>8506.225806451614</v>
       </c>
       <c r="C108" t="n">
-        <v>42766667754.27766</v>
+        <v>438417000</v>
       </c>
     </row>
     <row r="109">
@@ -2001,7 +2001,7 @@
         <v>20799.36666666666</v>
       </c>
       <c r="C109" t="n">
-        <v>48378555897.5914</v>
+        <v>390746142.1052632</v>
       </c>
     </row>
     <row r="110">
@@ -2012,7 +2012,7 @@
         <v>6610.064516129032</v>
       </c>
       <c r="C110" t="n">
-        <v>35004278763.2421</v>
+        <v>291156300</v>
       </c>
     </row>
     <row r="111">
@@ -2023,7 +2023,7 @@
         <v>8099.516129032259</v>
       </c>
       <c r="C111" t="n">
-        <v>42578842389.77814</v>
+        <v>368425809.0909091</v>
       </c>
     </row>
     <row r="112">
@@ -2034,7 +2034,7 @@
         <v>6939.6</v>
       </c>
       <c r="C112" t="n">
-        <v>35817076481.33392</v>
+        <v>313558160</v>
       </c>
     </row>
     <row r="113">
@@ -2045,7 +2045,7 @@
         <v>7433.806451612903</v>
       </c>
       <c r="C113" t="n">
-        <v>32600565649.69154</v>
+        <v>244692052.173913</v>
       </c>
     </row>
     <row r="114">
@@ -2056,7 +2056,7 @@
         <v>9167.799999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>31985012267.4627</v>
+        <v>224870730</v>
       </c>
     </row>
     <row r="115">
@@ -2067,7 +2067,7 @@
         <v>7653.322580645161</v>
       </c>
       <c r="C115" t="n">
-        <v>26515687818.22706</v>
+        <v>194564533.3333333</v>
       </c>
     </row>
     <row r="116">
@@ -2078,7 +2078,7 @@
         <v>14017.22580645161</v>
       </c>
       <c r="C116" t="n">
-        <v>39289486511.36562</v>
+        <v>297420040</v>
       </c>
     </row>
     <row r="117">
@@ -2089,7 +2089,7 @@
         <v>7292.892857142857</v>
       </c>
       <c r="C117" t="n">
-        <v>32133024447.99046</v>
+        <v>250275284.2105263</v>
       </c>
     </row>
     <row r="118">
@@ -2100,7 +2100,7 @@
         <v>5586.193548387097</v>
       </c>
       <c r="C118" t="n">
-        <v>33609222854.53938</v>
+        <v>294188109.5238096</v>
       </c>
     </row>
     <row r="119">
@@ -2111,7 +2111,7 @@
         <v>6057.533333333334</v>
       </c>
       <c r="C119" t="n">
-        <v>33845541809.23596</v>
+        <v>324333638.0952381</v>
       </c>
     </row>
     <row r="120">
@@ -2122,7 +2122,7 @@
         <v>4955.83870967742</v>
       </c>
       <c r="C120" t="n">
-        <v>29082741672.72074</v>
+        <v>226514466.6666667</v>
       </c>
     </row>
     <row r="121">
@@ -2133,7 +2133,7 @@
         <v>4150.066666666667</v>
       </c>
       <c r="C121" t="n">
-        <v>27853411119.15093</v>
+        <v>191064840</v>
       </c>
     </row>
     <row r="122">
@@ -2144,7 +2144,7 @@
         <v>9500.548387096775</v>
       </c>
       <c r="C122" t="n">
-        <v>27389921193.10247</v>
+        <v>163491109.0909091</v>
       </c>
     </row>
     <row r="123">
@@ -2155,7 +2155,7 @@
         <v>7495.870967741936</v>
       </c>
       <c r="C123" t="n">
-        <v>30709051255.2948</v>
+        <v>171851961.9047619</v>
       </c>
     </row>
     <row r="124">
@@ -2166,7 +2166,7 @@
         <v>6704.133333333333</v>
       </c>
       <c r="C124" t="n">
-        <v>32524643145.8273</v>
+        <v>185261680.952381</v>
       </c>
     </row>
     <row r="125">
@@ -2177,7 +2177,7 @@
         <v>10377.61290322581</v>
       </c>
       <c r="C125" t="n">
-        <v>33105939936.52052</v>
+        <v>175261626.0869565</v>
       </c>
     </row>
     <row r="126">
@@ -2188,7 +2188,7 @@
         <v>12848.83333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>40842150158.30857</v>
+        <v>218955173.6842105</v>
       </c>
     </row>
     <row r="127">
@@ -2199,7 +2199,7 @@
         <v>7957.709677419355</v>
       </c>
       <c r="C127" t="n">
-        <v>29884819259.77242</v>
+        <v>164986077.2727273</v>
       </c>
     </row>
     <row r="128">
@@ -2210,7 +2210,7 @@
         <v>7034.967741935484</v>
       </c>
       <c r="C128" t="n">
-        <v>30639420705.97175</v>
+        <v>164611430</v>
       </c>
     </row>
     <row r="129">
@@ -2221,7 +2221,7 @@
         <v>6380.107142857143</v>
       </c>
       <c r="C129" t="n">
-        <v>36431005459.34392</v>
+        <v>197128684.2105263</v>
       </c>
     </row>
     <row r="130">
@@ -2232,7 +2232,7 @@
         <v>5631.548387096775</v>
       </c>
       <c r="C130" t="n">
-        <v>32571482282.69625</v>
+        <v>183052309.0909091</v>
       </c>
     </row>
     <row r="131">
@@ -2243,7 +2243,7 @@
         <v>5246.2</v>
       </c>
       <c r="C131" t="n">
-        <v>29150169535.32889</v>
+        <v>149026128.5714286</v>
       </c>
     </row>
     <row r="132">
@@ -2254,7 +2254,7 @@
         <v>8993.58064516129</v>
       </c>
       <c r="C132" t="n">
-        <v>35830645888.7809</v>
+        <v>166242035</v>
       </c>
     </row>
     <row r="133">
@@ -2265,7 +2265,7 @@
         <v>6701.033333333334</v>
       </c>
       <c r="C133" t="n">
-        <v>33735294920.33706</v>
+        <v>163062204.7619048</v>
       </c>
     </row>
     <row r="134">
@@ -2276,7 +2276,7 @@
         <v>5407.806451612903</v>
       </c>
       <c r="C134" t="n">
-        <v>26219952618.65956</v>
+        <v>129663427.2727273</v>
       </c>
     </row>
     <row r="135">
@@ -2287,18 +2287,7 @@
         <v>4971.064516129032</v>
       </c>
       <c r="C135" t="n">
-        <v>27850207976.35476</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B136" t="n">
-        <v>5725</v>
-      </c>
-      <c r="C136" t="n">
-        <v>24962536081.27495</v>
+        <v>127744447.6190476</v>
       </c>
     </row>
   </sheetData>
@@ -34990,11 +34979,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35005,7 +34994,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>NVDA dollar volume ($/day, avg)</t>
+          <t>NVDA shares traded (per day, avg)</t>
         </is>
       </c>
     </row>
@@ -35014,7 +35003,7 @@
         <v>42186</v>
       </c>
       <c r="B2" t="n">
-        <v>119176737.0071465</v>
+        <v>249109272.7272727</v>
       </c>
     </row>
     <row r="3">
@@ -35022,7 +35011,7 @@
         <v>42217</v>
       </c>
       <c r="B3" t="n">
-        <v>241792640.3872172</v>
+        <v>450928190.4761904</v>
       </c>
     </row>
     <row r="4">
@@ -35030,7 +35019,7 @@
         <v>42248</v>
       </c>
       <c r="B4" t="n">
-        <v>172128030.513173</v>
+        <v>308581333.3333333</v>
       </c>
     </row>
     <row r="5">
@@ -35038,7 +35027,7 @@
         <v>42278</v>
       </c>
       <c r="B5" t="n">
-        <v>238658506.1465502</v>
+        <v>366014363.6363636</v>
       </c>
     </row>
     <row r="6">
@@ -35046,7 +35035,7 @@
         <v>42309</v>
       </c>
       <c r="B6" t="n">
-        <v>271074534.4281673</v>
+        <v>367240800</v>
       </c>
     </row>
     <row r="7">
@@ -35054,7 +35043,7 @@
         <v>42339</v>
       </c>
       <c r="B7" t="n">
-        <v>204999180.6225777</v>
+        <v>255780545.4545455</v>
       </c>
     </row>
     <row r="8">
@@ -35062,7 +35051,7 @@
         <v>42370</v>
       </c>
       <c r="B8" t="n">
-        <v>304536300.5475119</v>
+        <v>428367368.4210526</v>
       </c>
     </row>
     <row r="9">
@@ -35070,7 +35059,7 @@
         <v>42401</v>
       </c>
       <c r="B9" t="n">
-        <v>312717808.2038879</v>
+        <v>450002400</v>
       </c>
     </row>
     <row r="10">
@@ -35078,7 +35067,7 @@
         <v>42430</v>
       </c>
       <c r="B10" t="n">
-        <v>244389643.8930793</v>
+        <v>298995636.3636364</v>
       </c>
     </row>
     <row r="11">
@@ -35086,7 +35075,7 @@
         <v>42461</v>
       </c>
       <c r="B11" t="n">
-        <v>283940229.4481141</v>
+        <v>320678666.6666667</v>
       </c>
     </row>
     <row r="12">
@@ -35094,7 +35083,7 @@
         <v>42491</v>
       </c>
       <c r="B12" t="n">
-        <v>493459851.9519965</v>
+        <v>493706476.1904762</v>
       </c>
     </row>
     <row r="13">
@@ -35102,7 +35091,7 @@
         <v>42522</v>
       </c>
       <c r="B13" t="n">
-        <v>425646461.7016532</v>
+        <v>372631818.1818182</v>
       </c>
     </row>
     <row r="14">
@@ -35110,7 +35099,7 @@
         <v>42552</v>
       </c>
       <c r="B14" t="n">
-        <v>467127451.218462</v>
+        <v>360502600</v>
       </c>
     </row>
     <row r="15">
@@ -35118,7 +35107,7 @@
         <v>42583</v>
       </c>
       <c r="B15" t="n">
-        <v>602732021.942968</v>
+        <v>404570434.7826087</v>
       </c>
     </row>
     <row r="16">
@@ -35126,7 +35115,7 @@
         <v>42614</v>
       </c>
       <c r="B16" t="n">
-        <v>640112893.6097054</v>
+        <v>412631047.6190476</v>
       </c>
     </row>
     <row r="17">
@@ -35134,7 +35123,7 @@
         <v>42644</v>
       </c>
       <c r="B17" t="n">
-        <v>522120957.7855837</v>
+        <v>311979428.5714286</v>
       </c>
     </row>
     <row r="18">
@@ -35142,7 +35131,7 @@
         <v>42675</v>
       </c>
       <c r="B18" t="n">
-        <v>1252364820.939087</v>
+        <v>607974476.1904762</v>
       </c>
     </row>
     <row r="19">
@@ -35150,7 +35139,7 @@
         <v>42705</v>
       </c>
       <c r="B19" t="n">
-        <v>2170773464.907056</v>
+        <v>861058476.1904762</v>
       </c>
     </row>
     <row r="20">
@@ -35158,7 +35147,7 @@
         <v>42736</v>
       </c>
       <c r="B20" t="n">
-        <v>1727593753.759003</v>
+        <v>669842000</v>
       </c>
     </row>
     <row r="21">
@@ -35166,7 +35155,7 @@
         <v>42767</v>
       </c>
       <c r="B21" t="n">
-        <v>2012906071.050644</v>
+        <v>747725684.2105263</v>
       </c>
     </row>
     <row r="22">
@@ -35174,7 +35163,7 @@
         <v>42795</v>
       </c>
       <c r="B22" t="n">
-        <v>1582464114.376856</v>
+        <v>621259130.4347826</v>
       </c>
     </row>
     <row r="23">
@@ -35182,7 +35171,7 @@
         <v>42826</v>
       </c>
       <c r="B23" t="n">
-        <v>1248475607.773781</v>
+        <v>503819578.9473684</v>
       </c>
     </row>
     <row r="24">
@@ -35190,7 +35179,7 @@
         <v>42856</v>
       </c>
       <c r="B24" t="n">
-        <v>2766373599.863963</v>
+        <v>873156545.4545455</v>
       </c>
     </row>
     <row r="25">
@@ -35198,7 +35187,7 @@
         <v>42887</v>
       </c>
       <c r="B25" t="n">
-        <v>3969353568.35647</v>
+        <v>1065705454.545455</v>
       </c>
     </row>
     <row r="26">
@@ -35206,7 +35195,7 @@
         <v>42917</v>
       </c>
       <c r="B26" t="n">
-        <v>3037885000.704908</v>
+        <v>774550800</v>
       </c>
     </row>
     <row r="27">
@@ -35214,7 +35203,7 @@
         <v>42948</v>
       </c>
       <c r="B27" t="n">
-        <v>2603482797.420419</v>
+        <v>640357217.3913044</v>
       </c>
     </row>
     <row r="28">
@@ -35222,7 +35211,7 @@
         <v>42979</v>
       </c>
       <c r="B28" t="n">
-        <v>3139738921.092033</v>
+        <v>722366800</v>
       </c>
     </row>
     <row r="29">
@@ -35230,7 +35219,7 @@
         <v>43009</v>
       </c>
       <c r="B29" t="n">
-        <v>2467356088.232561</v>
+        <v>519212000</v>
       </c>
     </row>
     <row r="30">
@@ -35238,7 +35227,7 @@
         <v>43040</v>
       </c>
       <c r="B30" t="n">
-        <v>2902427293.988728</v>
+        <v>563376000</v>
       </c>
     </row>
     <row r="31">
@@ -35246,7 +35235,7 @@
         <v>43070</v>
       </c>
       <c r="B31" t="n">
-        <v>2395161410.512543</v>
+        <v>505610800</v>
       </c>
     </row>
     <row r="32">
@@ -35254,7 +35243,7 @@
         <v>43101</v>
       </c>
       <c r="B32" t="n">
-        <v>3053681058.660235</v>
+        <v>545534095.2380953</v>
       </c>
     </row>
     <row r="33">
@@ -35262,7 +35251,7 @@
         <v>43132</v>
       </c>
       <c r="B33" t="n">
-        <v>4529898829.469781</v>
+        <v>785027789.4736842</v>
       </c>
     </row>
     <row r="34">
@@ -35270,7 +35259,7 @@
         <v>43160</v>
       </c>
       <c r="B34" t="n">
-        <v>3955656275.772549</v>
+        <v>672306666.6666666</v>
       </c>
     </row>
     <row r="35">
@@ -35278,7 +35267,7 @@
         <v>43191</v>
       </c>
       <c r="B35" t="n">
-        <v>2951766859.723591</v>
+        <v>530667047.6190476</v>
       </c>
     </row>
     <row r="36">
@@ -35286,7 +35275,7 @@
         <v>43221</v>
       </c>
       <c r="B36" t="n">
-        <v>3336711199.892044</v>
+        <v>544465454.5454545</v>
       </c>
     </row>
     <row r="37">
@@ -35294,7 +35283,7 @@
         <v>43252</v>
       </c>
       <c r="B37" t="n">
-        <v>2643527824.292228</v>
+        <v>418359047.6190476</v>
       </c>
     </row>
     <row r="38">
@@ -35302,7 +35291,7 @@
         <v>43282</v>
       </c>
       <c r="B38" t="n">
-        <v>1849653192.506699</v>
+        <v>301041714.2857143</v>
       </c>
     </row>
     <row r="39">
@@ -35310,7 +35299,7 @@
         <v>43313</v>
       </c>
       <c r="B39" t="n">
-        <v>3048666656.494804</v>
+        <v>474688521.7391304</v>
       </c>
     </row>
     <row r="40">
@@ -35318,7 +35307,7 @@
         <v>43344</v>
       </c>
       <c r="B40" t="n">
-        <v>2246803847.557971</v>
+        <v>333694736.8421053</v>
       </c>
     </row>
     <row r="41">
@@ -35326,7 +35315,7 @@
         <v>43374</v>
       </c>
       <c r="B41" t="n">
-        <v>3244947761.08294</v>
+        <v>564259826.0869565</v>
       </c>
     </row>
     <row r="42">
@@ -35334,7 +35323,7 @@
         <v>43405</v>
       </c>
       <c r="B42" t="n">
-        <v>3270224467.369715</v>
+        <v>769635238.0952381</v>
       </c>
     </row>
     <row r="43">
@@ -35342,7 +35331,7 @@
         <v>43435</v>
       </c>
       <c r="B43" t="n">
-        <v>2339058537.711595</v>
+        <v>655337263.1578947</v>
       </c>
     </row>
     <row r="44">
@@ -35350,7 +35339,7 @@
         <v>43466</v>
       </c>
       <c r="B44" t="n">
-        <v>2863801396.408808</v>
+        <v>803380571.4285715</v>
       </c>
     </row>
     <row r="45">
@@ -35358,7 +35347,7 @@
         <v>43497</v>
       </c>
       <c r="B45" t="n">
-        <v>2286165061.585979</v>
+        <v>602406736.8421053</v>
       </c>
     </row>
     <row r="46">
@@ -35366,7 +35355,7 @@
         <v>43525</v>
       </c>
       <c r="B46" t="n">
-        <v>2403666241.122518</v>
+        <v>574692380.9523809</v>
       </c>
     </row>
     <row r="47">
@@ -35374,7 +35363,7 @@
         <v>43556</v>
       </c>
       <c r="B47" t="n">
-        <v>2077829157.717659</v>
+        <v>449418095.2380952</v>
       </c>
     </row>
     <row r="48">
@@ -35382,7 +35371,7 @@
         <v>43586</v>
       </c>
       <c r="B48" t="n">
-        <v>2008990674.879247</v>
+        <v>508216000</v>
       </c>
     </row>
     <row r="49">
@@ -35390,7 +35379,7 @@
         <v>43617</v>
       </c>
       <c r="B49" t="n">
-        <v>1526350614.668512</v>
+        <v>411667000</v>
       </c>
     </row>
     <row r="50">
@@ -35398,7 +35387,7 @@
         <v>43647</v>
       </c>
       <c r="B50" t="n">
-        <v>1589365146.042911</v>
+        <v>382544727.2727273</v>
       </c>
     </row>
     <row r="51">
@@ -35406,7 +35395,7 @@
         <v>43678</v>
       </c>
       <c r="B51" t="n">
-        <v>1709685168.141712</v>
+        <v>429560363.6363636</v>
       </c>
     </row>
     <row r="52">
@@ -35414,7 +35403,7 @@
         <v>43709</v>
       </c>
       <c r="B52" t="n">
-        <v>1398975225.697899</v>
+        <v>317388400</v>
       </c>
     </row>
     <row r="53">
@@ -35422,7 +35411,7 @@
         <v>43739</v>
       </c>
       <c r="B53" t="n">
-        <v>1578080635.129348</v>
+        <v>334616173.9130435</v>
       </c>
     </row>
     <row r="54">
@@ -35430,7 +35419,7 @@
         <v>43770</v>
       </c>
       <c r="B54" t="n">
-        <v>1909638760.464764</v>
+        <v>366090000</v>
       </c>
     </row>
     <row r="55">
@@ -35438,7 +35427,7 @@
         <v>43800</v>
       </c>
       <c r="B55" t="n">
-        <v>1741241886.876606</v>
+        <v>311596761.9047619</v>
       </c>
     </row>
     <row r="56">
@@ -35446,7 +35435,7 @@
         <v>43831</v>
       </c>
       <c r="B56" t="n">
-        <v>1772561646.208264</v>
+        <v>291686285.7142857</v>
       </c>
     </row>
     <row r="57">
@@ -35454,7 +35443,7 @@
         <v>43862</v>
       </c>
       <c r="B57" t="n">
-        <v>4268220182.537079</v>
+        <v>623613263.1578947</v>
       </c>
     </row>
     <row r="58">
@@ -35462,7 +35451,7 @@
         <v>43891</v>
       </c>
       <c r="B58" t="n">
-        <v>4310317335.106243</v>
+        <v>716997818.1818181</v>
       </c>
     </row>
     <row r="59">
@@ -35470,7 +35459,7 @@
         <v>43922</v>
       </c>
       <c r="B59" t="n">
-        <v>3663569546.119599</v>
+        <v>537062095.2380953</v>
       </c>
     </row>
     <row r="60">
@@ -35478,7 +35467,7 @@
         <v>43952</v>
       </c>
       <c r="B60" t="n">
-        <v>5221682370.371246</v>
+        <v>627443800</v>
       </c>
     </row>
     <row r="61">
@@ -35486,7 +35475,7 @@
         <v>43983</v>
       </c>
       <c r="B61" t="n">
-        <v>4001159629.920266</v>
+        <v>441793818.1818182</v>
       </c>
     </row>
     <row r="62">
@@ -35494,7 +35483,7 @@
         <v>44013</v>
       </c>
       <c r="B62" t="n">
-        <v>3743314088.924234</v>
+        <v>367929636.3636364</v>
       </c>
     </row>
     <row r="63">
@@ -35502,7 +35491,7 @@
         <v>44044</v>
       </c>
       <c r="B63" t="n">
-        <v>5538476063.250587</v>
+        <v>460597333.3333333</v>
       </c>
     </row>
     <row r="64">
@@ -35510,7 +35499,7 @@
         <v>44075</v>
       </c>
       <c r="B64" t="n">
-        <v>9591020034.210024</v>
+        <v>755073904.7619047</v>
       </c>
     </row>
     <row r="65">
@@ -35518,7 +35507,7 @@
         <v>44105</v>
       </c>
       <c r="B65" t="n">
-        <v>4914765573.11873</v>
+        <v>364652545.4545454</v>
       </c>
     </row>
     <row r="66">
@@ -35526,7 +35515,7 @@
         <v>44136</v>
       </c>
       <c r="B66" t="n">
-        <v>5055653229.122925</v>
+        <v>379741000</v>
       </c>
     </row>
     <row r="67">
@@ -35534,7 +35523,7 @@
         <v>44166</v>
       </c>
       <c r="B67" t="n">
-        <v>3064972020.195354</v>
+        <v>232772545.4545455</v>
       </c>
     </row>
     <row r="68">
@@ -35542,7 +35531,7 @@
         <v>44197</v>
       </c>
       <c r="B68" t="n">
-        <v>4272179455.635673</v>
+        <v>323903789.4736842</v>
       </c>
     </row>
     <row r="69">
@@ -35550,7 +35539,7 @@
         <v>44228</v>
       </c>
       <c r="B69" t="n">
-        <v>4993958986.845518</v>
+        <v>351596000</v>
       </c>
     </row>
     <row r="70">
@@ -35558,7 +35547,7 @@
         <v>44256</v>
       </c>
       <c r="B70" t="n">
-        <v>4230832190.56005</v>
+        <v>332550260.8695652</v>
       </c>
     </row>
     <row r="71">
@@ -35566,7 +35555,7 @@
         <v>44287</v>
       </c>
       <c r="B71" t="n">
-        <v>4821919007.947468</v>
+        <v>319942666.6666667</v>
       </c>
     </row>
     <row r="72">
@@ -35574,7 +35563,7 @@
         <v>44317</v>
       </c>
       <c r="B72" t="n">
-        <v>5226246439.409256</v>
+        <v>352719000</v>
       </c>
     </row>
     <row r="73">
@@ -35582,7 +35571,7 @@
         <v>44348</v>
       </c>
       <c r="B73" t="n">
-        <v>8455848799.906297</v>
+        <v>466967818.1818182</v>
       </c>
     </row>
     <row r="74">
@@ -35590,7 +35579,7 @@
         <v>44378</v>
       </c>
       <c r="B74" t="n">
-        <v>7250315233.622869</v>
+        <v>372527476.1904762</v>
       </c>
     </row>
     <row r="75">
@@ -35598,7 +35587,7 @@
         <v>44409</v>
       </c>
       <c r="B75" t="n">
-        <v>6041826386.172901</v>
+        <v>291653909.0909091</v>
       </c>
     </row>
     <row r="76">
@@ -35606,7 +35595,7 @@
         <v>44440</v>
       </c>
       <c r="B76" t="n">
-        <v>5187963508.786974</v>
+        <v>238046952.3809524</v>
       </c>
     </row>
     <row r="77">
@@ -35614,7 +35603,7 @@
         <v>44470</v>
       </c>
       <c r="B77" t="n">
-        <v>5246804111.124493</v>
+        <v>236718000</v>
       </c>
     </row>
     <row r="78">
@@ -35622,7 +35611,7 @@
         <v>44501</v>
       </c>
       <c r="B78" t="n">
-        <v>15717939150.24885</v>
+        <v>514817619.047619</v>
       </c>
     </row>
     <row r="79">
@@ -35630,7 +35619,7 @@
         <v>44531</v>
       </c>
       <c r="B79" t="n">
-        <v>14946669691.22011</v>
+        <v>502659318.1818182</v>
       </c>
     </row>
     <row r="80">
@@ -35638,7 +35627,7 @@
         <v>44562</v>
       </c>
       <c r="B80" t="n">
-        <v>13493538590.90481</v>
+        <v>534108200</v>
       </c>
     </row>
     <row r="81">
@@ -35646,7 +35635,7 @@
         <v>44593</v>
       </c>
       <c r="B81" t="n">
-        <v>13743048357.92401</v>
+        <v>560224736.8421053</v>
       </c>
     </row>
     <row r="82">
@@ -35654,7 +35643,7 @@
         <v>44621</v>
       </c>
       <c r="B82" t="n">
-        <v>12664921353.59582</v>
+        <v>506286913.0434783</v>
       </c>
     </row>
     <row r="83">
@@ -35662,7 +35651,7 @@
         <v>44652</v>
       </c>
       <c r="B83" t="n">
-        <v>12069929531.71988</v>
+        <v>555719500</v>
       </c>
     </row>
     <row r="84">
@@ -35670,7 +35659,7 @@
         <v>44682</v>
       </c>
       <c r="B84" t="n">
-        <v>11649542739.25881</v>
+        <v>658715285.7142857</v>
       </c>
     </row>
     <row r="85">
@@ -35678,7 +35667,7 @@
         <v>44713</v>
       </c>
       <c r="B85" t="n">
-        <v>8489482874.203092</v>
+        <v>502609095.2380952</v>
       </c>
     </row>
     <row r="86">
@@ -35686,7 +35675,7 @@
         <v>44743</v>
       </c>
       <c r="B86" t="n">
-        <v>8610809537.190723</v>
+        <v>528223800</v>
       </c>
     </row>
     <row r="87">
@@ -35694,7 +35683,7 @@
         <v>44774</v>
       </c>
       <c r="B87" t="n">
-        <v>9233110943.686735</v>
+        <v>524767304.3478261</v>
       </c>
     </row>
     <row r="88">
@@ -35702,7 +35691,7 @@
         <v>44805</v>
       </c>
       <c r="B88" t="n">
-        <v>8220307964.633487</v>
+        <v>625265619.0476191</v>
       </c>
     </row>
     <row r="89">
@@ -35710,7 +35699,7 @@
         <v>44835</v>
       </c>
       <c r="B89" t="n">
-        <v>7390134873.710088</v>
+        <v>597584619.0476191</v>
       </c>
     </row>
     <row r="90">
@@ -35718,7 +35707,7 @@
         <v>44866</v>
       </c>
       <c r="B90" t="n">
-        <v>7689883749.582563</v>
+        <v>504790619.047619</v>
       </c>
     </row>
     <row r="91">
@@ -35726,7 +35715,7 @@
         <v>44896</v>
       </c>
       <c r="B91" t="n">
-        <v>6933557571.203413</v>
+        <v>426007238.0952381</v>
       </c>
     </row>
     <row r="92">
@@ -35734,7 +35723,7 @@
         <v>44927</v>
       </c>
       <c r="B92" t="n">
-        <v>8221944728.960037</v>
+        <v>472748000</v>
       </c>
     </row>
     <row r="93">
@@ -35742,7 +35731,7 @@
         <v>44958</v>
       </c>
       <c r="B93" t="n">
-        <v>12078125594.63622</v>
+        <v>547025210.5263158</v>
       </c>
     </row>
     <row r="94">
@@ -35750,7 +35739,7 @@
         <v>44986</v>
       </c>
       <c r="B94" t="n">
-        <v>12270776759.34808</v>
+        <v>489727434.7826087</v>
       </c>
     </row>
     <row r="95">
@@ -35758,7 +35747,7 @@
         <v>45017</v>
       </c>
       <c r="B95" t="n">
-        <v>10592546983.15068</v>
+        <v>391392105.2631579</v>
       </c>
     </row>
     <row r="96">
@@ -35766,7 +35755,7 @@
         <v>45047</v>
       </c>
       <c r="B96" t="n">
-        <v>17384081108.25114</v>
+        <v>531719045.4545454</v>
       </c>
     </row>
     <row r="97">
@@ -35774,7 +35763,7 @@
         <v>45078</v>
       </c>
       <c r="B97" t="n">
-        <v>20510416617.15553</v>
+        <v>501288095.2380952</v>
       </c>
     </row>
     <row r="98">
@@ -35782,7 +35771,7 @@
         <v>45108</v>
       </c>
       <c r="B98" t="n">
-        <v>19516666394.23046</v>
+        <v>435342250</v>
       </c>
     </row>
     <row r="99">
@@ -35790,7 +35779,7 @@
         <v>45139</v>
       </c>
       <c r="B99" t="n">
-        <v>26892085282.89082</v>
+        <v>592702260.8695652</v>
       </c>
     </row>
     <row r="100">
@@ -35798,7 +35787,7 @@
         <v>45170</v>
       </c>
       <c r="B100" t="n">
-        <v>18956786256.3139</v>
+        <v>428963650</v>
       </c>
     </row>
     <row r="101">
@@ -35806,7 +35795,7 @@
         <v>45200</v>
       </c>
       <c r="B101" t="n">
-        <v>20004110873.25478</v>
+        <v>460959136.3636364</v>
       </c>
     </row>
     <row r="102">
@@ -35814,7 +35803,7 @@
         <v>45231</v>
       </c>
       <c r="B102" t="n">
-        <v>20662350889.41992</v>
+        <v>435458000</v>
       </c>
     </row>
     <row r="103">
@@ -35822,7 +35811,7 @@
         <v>45261</v>
       </c>
       <c r="B103" t="n">
-        <v>17729040188.06858</v>
+        <v>370594350</v>
       </c>
     </row>
     <row r="104">
@@ -35830,7 +35819,7 @@
         <v>45292</v>
       </c>
       <c r="B104" t="n">
-        <v>25939419759.39923</v>
+        <v>462201761.9047619</v>
       </c>
     </row>
     <row r="105">
@@ -35838,7 +35827,7 @@
         <v>45323</v>
       </c>
       <c r="B105" t="n">
-        <v>40100317471.08879</v>
+        <v>553067800</v>
       </c>
     </row>
     <row r="106">
@@ -35846,7 +35835,7 @@
         <v>45352</v>
       </c>
       <c r="B106" t="n">
-        <v>54116072605.90096</v>
+        <v>607460900</v>
       </c>
     </row>
     <row r="107">
@@ -35854,7 +35843,7 @@
         <v>45383</v>
       </c>
       <c r="B107" t="n">
-        <v>38842932353.45078</v>
+        <v>457833363.6363636</v>
       </c>
     </row>
     <row r="108">
@@ -35862,7 +35851,7 @@
         <v>45413</v>
       </c>
       <c r="B108" t="n">
-        <v>42766667754.27766</v>
+        <v>438417000</v>
       </c>
     </row>
     <row r="109">
@@ -35870,7 +35859,7 @@
         <v>45444</v>
       </c>
       <c r="B109" t="n">
-        <v>48378555897.5914</v>
+        <v>390746142.1052632</v>
       </c>
     </row>
     <row r="110">
@@ -35878,7 +35867,7 @@
         <v>45474</v>
       </c>
       <c r="B110" t="n">
-        <v>35004278763.2421</v>
+        <v>291156300</v>
       </c>
     </row>
     <row r="111">
@@ -35886,7 +35875,7 @@
         <v>45505</v>
       </c>
       <c r="B111" t="n">
-        <v>42578842389.77814</v>
+        <v>368425809.0909091</v>
       </c>
     </row>
     <row r="112">
@@ -35894,7 +35883,7 @@
         <v>45536</v>
       </c>
       <c r="B112" t="n">
-        <v>35817076481.33392</v>
+        <v>313558160</v>
       </c>
     </row>
     <row r="113">
@@ -35902,7 +35891,7 @@
         <v>45566</v>
       </c>
       <c r="B113" t="n">
-        <v>32600565649.69154</v>
+        <v>244692052.173913</v>
       </c>
     </row>
     <row r="114">
@@ -35910,7 +35899,7 @@
         <v>45597</v>
       </c>
       <c r="B114" t="n">
-        <v>31985012267.4627</v>
+        <v>224870730</v>
       </c>
     </row>
     <row r="115">
@@ -35918,7 +35907,7 @@
         <v>45627</v>
       </c>
       <c r="B115" t="n">
-        <v>26515687818.22706</v>
+        <v>194564533.3333333</v>
       </c>
     </row>
     <row r="116">
@@ -35926,7 +35915,7 @@
         <v>45658</v>
       </c>
       <c r="B116" t="n">
-        <v>39289486511.36562</v>
+        <v>297420040</v>
       </c>
     </row>
     <row r="117">
@@ -35934,7 +35923,7 @@
         <v>45689</v>
       </c>
       <c r="B117" t="n">
-        <v>32133024447.99046</v>
+        <v>250275284.2105263</v>
       </c>
     </row>
     <row r="118">
@@ -35942,7 +35931,7 @@
         <v>45717</v>
       </c>
       <c r="B118" t="n">
-        <v>33609222854.53938</v>
+        <v>294188109.5238096</v>
       </c>
     </row>
     <row r="119">
@@ -35950,7 +35939,7 @@
         <v>45748</v>
       </c>
       <c r="B119" t="n">
-        <v>33845541809.23596</v>
+        <v>324333638.0952381</v>
       </c>
     </row>
     <row r="120">
@@ -35958,7 +35947,7 @@
         <v>45778</v>
       </c>
       <c r="B120" t="n">
-        <v>29082741672.72074</v>
+        <v>226514466.6666667</v>
       </c>
     </row>
     <row r="121">
@@ -35966,7 +35955,7 @@
         <v>45809</v>
       </c>
       <c r="B121" t="n">
-        <v>27853411119.15093</v>
+        <v>191064840</v>
       </c>
     </row>
     <row r="122">
@@ -35974,7 +35963,7 @@
         <v>45839</v>
       </c>
       <c r="B122" t="n">
-        <v>27389921193.10247</v>
+        <v>163491109.0909091</v>
       </c>
     </row>
     <row r="123">
@@ -35982,7 +35971,7 @@
         <v>45870</v>
       </c>
       <c r="B123" t="n">
-        <v>30709051255.2948</v>
+        <v>171851961.9047619</v>
       </c>
     </row>
     <row r="124">
@@ -35990,7 +35979,7 @@
         <v>45901</v>
       </c>
       <c r="B124" t="n">
-        <v>32524643145.8273</v>
+        <v>185261680.952381</v>
       </c>
     </row>
     <row r="125">
@@ -35998,7 +35987,7 @@
         <v>45931</v>
       </c>
       <c r="B125" t="n">
-        <v>33105939936.52052</v>
+        <v>175261626.0869565</v>
       </c>
     </row>
     <row r="126">
@@ -36006,7 +35995,7 @@
         <v>45962</v>
       </c>
       <c r="B126" t="n">
-        <v>40842150158.30857</v>
+        <v>218955173.6842105</v>
       </c>
     </row>
     <row r="127">
@@ -36014,7 +36003,7 @@
         <v>45992</v>
       </c>
       <c r="B127" t="n">
-        <v>29884819259.77242</v>
+        <v>164986077.2727273</v>
       </c>
     </row>
     <row r="128">
@@ -36022,7 +36011,7 @@
         <v>46023</v>
       </c>
       <c r="B128" t="n">
-        <v>30639420705.97175</v>
+        <v>164611430</v>
       </c>
     </row>
     <row r="129">
@@ -36030,7 +36019,7 @@
         <v>46054</v>
       </c>
       <c r="B129" t="n">
-        <v>36431005459.34392</v>
+        <v>197128684.2105263</v>
       </c>
     </row>
     <row r="130">
@@ -36038,7 +36027,7 @@
         <v>46082</v>
       </c>
       <c r="B130" t="n">
-        <v>32571482282.69625</v>
+        <v>183052309.0909091</v>
       </c>
     </row>
     <row r="131">
@@ -36046,7 +36035,7 @@
         <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>29150169535.32889</v>
+        <v>149026128.5714286</v>
       </c>
     </row>
     <row r="132">
@@ -36054,7 +36043,7 @@
         <v>46143</v>
       </c>
       <c r="B132" t="n">
-        <v>35830645888.7809</v>
+        <v>166242035</v>
       </c>
     </row>
     <row r="133">
@@ -36062,7 +36051,7 @@
         <v>46174</v>
       </c>
       <c r="B133" t="n">
-        <v>33735294920.33706</v>
+        <v>163062204.7619048</v>
       </c>
     </row>
     <row r="134">
@@ -36070,7 +36059,7 @@
         <v>46204</v>
       </c>
       <c r="B134" t="n">
-        <v>26219952618.65956</v>
+        <v>129663427.2727273</v>
       </c>
     </row>
     <row r="135">
@@ -36078,15 +36067,7 @@
         <v>46235</v>
       </c>
       <c r="B135" t="n">
-        <v>27850207976.35476</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B136" t="n">
-        <v>24962536081.27495</v>
+        <v>127744447.6190476</v>
       </c>
     </row>
   </sheetData>
@@ -36104,8 +36085,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -36148,14 +36129,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.03869, 2.64514</t>
+          <t>-0.283452, 9.58547</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7627</v>
+        <v>0.1664</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7609</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="3">
@@ -36169,14 +36150,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.64325, 21.0419, -31.2713</t>
+          <t>-0.0734595, 0.244799, 8.64248</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8683</v>
+        <v>0.1673</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8663</v>
+        <v>0.1546</v>
       </c>
     </row>
     <row r="4">
@@ -36190,14 +36171,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.69301, -32.1493, 128.312, -160.675</t>
+          <t>2.58099, -28.3479, 103.02, -115.318</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8829</v>
+        <v>0.3193</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8803</v>
+        <v>0.3036</v>
       </c>
     </row>
     <row r="5">
@@ -36211,14 +36192,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.22745, 64.7291, -372.19, 953.479, -908.711</t>
+          <t>-2.36832, 37.3387, -218.884, 565.431, -534.539</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8858</v>
+        <v>0.3294</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8823</v>
+        <v>0.3086</v>
       </c>
     </row>
     <row r="6">
@@ -36235,7 +36216,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -36248,7 +36229,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8733</v>
+        <v>-0.4079</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -36261,7 +36242,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.260798596609114e-43</v>
+        <v>1.000409455694961e-06</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -36274,7 +36255,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.790695313710477e-18</v>
+        <v>0.01502059650856758</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -36288,7 +36269,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>log y = 2.04·log x + 2.65</t>
+          <t>log y = -0.283·log x + 9.59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>

--- a/006/xy_006_data.xlsx
+++ b/006/xy_006_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Attention Is All You Trade, Briefly</t>
+          <t>Nvidia Page Views vs Shares Traded</t>
         </is>
       </c>
     </row>
@@ -488,293 +488,281 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The more people read about Nvidia, the more of its shares change hands.</t>
+          <t>More readers, more trading.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Attention spikes bring trading spikes, not a lasting trading boom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>publication</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://xandyregression.substack.com</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X label</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wikipedia views of 'Nvidia' (daily avg)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X label</t>
+          <t>X detail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wikipedia views of 'Nvidia' (daily avg)</t>
+          <t>Daily pageviews of the English Wikipedia article 'Nvidia', averaged by month, Wikimedia REST API, 07/2015 - 08/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X detail</t>
+          <t>X source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daily pageviews of the English Wikipedia article 'Nvidia', averaged by month, Wikimedia REST API, 07/2015 - 08/2026</t>
+          <t>Wikipedia pageviews 'Nvidia'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X source</t>
+          <t>X source URL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wikipedia pageviews 'Nvidia'</t>
+          <t>https://wikimedia.org/api/rest_v1/metrics/pageviews/per-article/en.wikipedia/all-access/user/Nvidia/daily/2015070100/2026090100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X source URL</t>
+          <t>X licence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://wikimedia.org/api/rest_v1/metrics/pageviews/per-article/en.wikipedia/all-access/user/Nvidia/daily/2015070100/2026090100</t>
+          <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X licence</t>
+          <t>X pulled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>open data, redistributed with attribution</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X pulled</t>
+          <t>X steps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 02:04</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X steps</t>
+          <t>X raw sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
+        <is>
+          <t>full series as pulled, before any transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Y label</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NVDA shares traded (per day, avg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Y detail</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NVDA shares traded per day, split-adjusted, averaged by month, Yahoo Finance, 07/2015 - present</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Y source</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Yahoo Finance NVDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Y source URL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/NVDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Y licence</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>third-party data: only the aggregated values used are included, see source</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Y pulled</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>26/09/2026 19:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Y steps</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>X raw sheet</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>full series as pulled, before any transform</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Y label</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NVDA shares traded (per day, avg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Y detail</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NVDA shares traded per day, split-adjusted, averaged by month, Yahoo Finance, 07/2015 - present</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Y source</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Yahoo Finance NVDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Y source URL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/quote/NVDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Y licence</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>third-party data: only the aggregated values used are included, see source</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Y pulled</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>25/09/2026 02:04</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y steps</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
           <t>Y raw sheet</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>values used in the regression only (source licence); full series at source URL</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>join</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>resampled to M by mean</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>join</t>
+          <t>lag</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>resampled to M by mean</t>
+          <t>X leads Y by 0 periods</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lag</t>
+          <t>transform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>X leads Y by 0 periods</t>
+          <t>log_log</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>log_log</t>
+          <t>Newey-West (HAC) for time series</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Newey-West (HAC) for time series</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>correlation is not causation</t>
         </is>
